--- a/Data/2007_F111_CO_ISM/2007_F111_CO_ISM_SoilAnalysis.xlsx
+++ b/Data/2007_F111_CO_ISM/2007_F111_CO_ISM_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2007_F111_CO_ISM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02489893-2F25-468E-8D18-A50A8FBCF8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC35041-872F-4F50-BAF1-2045A87CB9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1665" yWindow="-27630" windowWidth="18210" windowHeight="20985" activeTab="2" xr2:uid="{CD3BE64E-F897-4A9D-ACFB-0EFCE357F42D}"/>
+    <workbookView xWindow="-1365" yWindow="-24645" windowWidth="17775" windowHeight="24285" xr2:uid="{CD3BE64E-F897-4A9D-ACFB-0EFCE357F42D}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -3267,58 +3267,58 @@
         <v>18.598886</v>
       </c>
       <c r="AK2">
-        <v>7.0583000000000007E-2</v>
+        <v>0.112943</v>
       </c>
       <c r="AL2">
-        <v>6.9106000000000001E-2</v>
+        <v>0.110598</v>
       </c>
       <c r="AM2">
-        <v>7.1657999999999999E-2</v>
+        <v>0.110208</v>
       </c>
       <c r="AN2">
-        <v>7.3567999999999995E-2</v>
+        <v>0.114215</v>
       </c>
       <c r="AO2">
-        <v>7.3084999999999997E-2</v>
+        <v>0.118879</v>
       </c>
       <c r="AP2">
-        <v>7.1979000000000001E-2</v>
+        <v>0.115144</v>
       </c>
       <c r="AQ2">
-        <v>8.3988999999999994E-2</v>
+        <v>0.13625100000000001</v>
       </c>
       <c r="AR2">
-        <v>7.9725000000000004E-2</v>
+        <v>0.12735399999999999</v>
       </c>
       <c r="AS2">
-        <v>7.3738999999999999E-2</v>
+        <v>0.12242500000000001</v>
       </c>
       <c r="AT2">
-        <v>8.7106000000000003E-2</v>
+        <v>0.137098</v>
       </c>
       <c r="AU2">
-        <v>8.6307999999999996E-2</v>
+        <v>0.142676</v>
       </c>
       <c r="AV2">
-        <v>8.3672999999999997E-2</v>
+        <v>0.133579</v>
       </c>
       <c r="AW2">
-        <v>0.13058800000000001</v>
+        <v>0.20991799999999999</v>
       </c>
       <c r="AX2">
-        <v>0.13245799999999999</v>
+        <v>0.21132200000000001</v>
       </c>
       <c r="AY2">
-        <v>0.12599399999999999</v>
+        <v>0.21016199999999999</v>
       </c>
       <c r="AZ2">
-        <v>0.145619</v>
+        <v>0.23903099999999999</v>
       </c>
       <c r="BA2">
-        <v>0.15121699999999999</v>
+        <v>0.24365500000000001</v>
       </c>
       <c r="BB2">
-        <v>0.14529500000000001</v>
+        <v>0.234042</v>
       </c>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.25">
@@ -3431,58 +3431,58 @@
         <v>13.454370000000001</v>
       </c>
       <c r="AK3">
-        <v>7.0580000000000004E-2</v>
+        <v>0.11293</v>
       </c>
       <c r="AL3">
-        <v>6.9602999999999998E-2</v>
+        <v>0.111389</v>
       </c>
       <c r="AM3">
-        <v>7.4749999999999997E-2</v>
+        <v>0.11927</v>
       </c>
       <c r="AN3">
-        <v>7.5342999999999993E-2</v>
+        <v>0.118727</v>
       </c>
       <c r="AO3">
-        <v>7.5327000000000005E-2</v>
+        <v>0.121238</v>
       </c>
       <c r="AP3">
-        <v>7.3122000000000006E-2</v>
+        <v>0.116967</v>
       </c>
       <c r="AQ3">
-        <v>8.3614999999999995E-2</v>
+        <v>0.13569500000000001</v>
       </c>
       <c r="AR3">
-        <v>7.8396999999999994E-2</v>
+        <v>0.12612699999999999</v>
       </c>
       <c r="AS3">
-        <v>7.9172999999999993E-2</v>
+        <v>0.129769</v>
       </c>
       <c r="AT3">
-        <v>8.7625999999999996E-2</v>
+        <v>0.13885400000000001</v>
       </c>
       <c r="AU3">
-        <v>9.1178999999999996E-2</v>
+        <v>0.14685300000000001</v>
       </c>
       <c r="AV3">
-        <v>8.3183999999999994E-2</v>
+        <v>0.133543</v>
       </c>
       <c r="AW3">
-        <v>0.133405</v>
+        <v>0.21338699999999999</v>
       </c>
       <c r="AX3">
-        <v>0.133795</v>
+        <v>0.213783</v>
       </c>
       <c r="AY3">
-        <v>0.140685</v>
+        <v>0.220364</v>
       </c>
       <c r="AZ3">
-        <v>0.151837</v>
+        <v>0.249719</v>
       </c>
       <c r="BA3">
-        <v>0.154723</v>
+        <v>0.24804000000000001</v>
       </c>
       <c r="BB3">
-        <v>0.141928</v>
+        <v>0.227243</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.25">
@@ -3595,58 +3595,58 @@
         <v>13.95462</v>
       </c>
       <c r="AK4">
-        <v>7.0829000000000003E-2</v>
+        <v>0.113318</v>
       </c>
       <c r="AL4">
-        <v>6.9712999999999997E-2</v>
+        <v>0.11157300000000001</v>
       </c>
       <c r="AM4">
-        <v>7.3387999999999995E-2</v>
+        <v>0.115508</v>
       </c>
       <c r="AN4">
-        <v>7.6180999999999999E-2</v>
+        <v>0.120239</v>
       </c>
       <c r="AO4">
-        <v>7.5742000000000004E-2</v>
+        <v>0.122004</v>
       </c>
       <c r="AP4">
-        <v>7.4163999999999994E-2</v>
+        <v>0.118571</v>
       </c>
       <c r="AQ4">
-        <v>8.2608000000000001E-2</v>
+        <v>0.13245299999999999</v>
       </c>
       <c r="AR4">
-        <v>7.7973000000000001E-2</v>
+        <v>0.126133</v>
       </c>
       <c r="AS4">
-        <v>7.5974E-2</v>
+        <v>0.12429</v>
       </c>
       <c r="AT4">
-        <v>8.8489999999999999E-2</v>
+        <v>0.140316</v>
       </c>
       <c r="AU4">
-        <v>9.3590999999999994E-2</v>
+        <v>0.14938000000000001</v>
       </c>
       <c r="AV4">
-        <v>8.4848999999999994E-2</v>
+        <v>0.135625</v>
       </c>
       <c r="AW4">
-        <v>0.133989</v>
+        <v>0.21435499999999999</v>
       </c>
       <c r="AX4">
-        <v>0.13411600000000001</v>
+        <v>0.21399000000000001</v>
       </c>
       <c r="AY4">
-        <v>0.132823</v>
+        <v>0.217394</v>
       </c>
       <c r="AZ4">
-        <v>0.152669</v>
+        <v>0.247586</v>
       </c>
       <c r="BA4">
-        <v>0.15646199999999999</v>
+        <v>0.25127300000000002</v>
       </c>
       <c r="BB4">
-        <v>0.142398</v>
+        <v>0.22796</v>
       </c>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.25">
@@ -3759,58 +3759,58 @@
         <v>15.983542</v>
       </c>
       <c r="AK5">
-        <v>7.0899000000000004E-2</v>
+        <v>0.113431</v>
       </c>
       <c r="AL5">
-        <v>7.1220000000000006E-2</v>
+        <v>0.113968</v>
       </c>
       <c r="AM5">
-        <v>7.3197999999999999E-2</v>
+        <v>0.114467</v>
       </c>
       <c r="AN5">
-        <v>7.8367999999999993E-2</v>
+        <v>0.124568</v>
       </c>
       <c r="AO5">
-        <v>7.6886999999999997E-2</v>
+        <v>0.12365900000000001</v>
       </c>
       <c r="AP5">
-        <v>7.3993000000000003E-2</v>
+        <v>0.11848</v>
       </c>
       <c r="AQ5">
-        <v>8.1844E-2</v>
+        <v>0.12966</v>
       </c>
       <c r="AR5">
-        <v>8.0309000000000005E-2</v>
+        <v>0.12895499999999999</v>
       </c>
       <c r="AS5">
-        <v>7.7740000000000004E-2</v>
+        <v>0.126471</v>
       </c>
       <c r="AT5">
-        <v>9.0957999999999997E-2</v>
+        <v>0.14536099999999999</v>
       </c>
       <c r="AU5">
-        <v>9.4103000000000006E-2</v>
+        <v>0.15084600000000001</v>
       </c>
       <c r="AV5">
-        <v>8.5855000000000001E-2</v>
+        <v>0.137188</v>
       </c>
       <c r="AW5">
-        <v>0.135134</v>
+        <v>0.21605099999999999</v>
       </c>
       <c r="AX5">
-        <v>0.13748099999999999</v>
+        <v>0.22009400000000001</v>
       </c>
       <c r="AY5">
-        <v>0.13747100000000001</v>
+        <v>0.224967</v>
       </c>
       <c r="AZ5">
-        <v>0.15964100000000001</v>
+        <v>0.25761699999999998</v>
       </c>
       <c r="BA5">
-        <v>0.16208400000000001</v>
+        <v>0.258716</v>
       </c>
       <c r="BB5">
-        <v>0.14389099999999999</v>
+        <v>0.23058500000000001</v>
       </c>
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.25">
@@ -3923,58 +3923,58 @@
         <v>17.237348000000001</v>
       </c>
       <c r="AK6">
-        <v>7.1125999999999995E-2</v>
+        <v>0.113789</v>
       </c>
       <c r="AL6">
-        <v>7.3619000000000004E-2</v>
+        <v>0.117775</v>
       </c>
       <c r="AM6">
-        <v>7.5671000000000002E-2</v>
+        <v>0.12010700000000001</v>
       </c>
       <c r="AN6">
-        <v>8.1638000000000002E-2</v>
+        <v>0.13131899999999999</v>
       </c>
       <c r="AO6">
-        <v>7.9936999999999994E-2</v>
+        <v>0.127246</v>
       </c>
       <c r="AP6">
-        <v>7.5245999999999993E-2</v>
+        <v>0.120423</v>
       </c>
       <c r="AQ6">
-        <v>8.2043000000000005E-2</v>
+        <v>0.130851</v>
       </c>
       <c r="AR6">
-        <v>8.4224999999999994E-2</v>
+        <v>0.133357</v>
       </c>
       <c r="AS6">
-        <v>8.6663000000000004E-2</v>
+        <v>0.139261</v>
       </c>
       <c r="AT6">
-        <v>9.3867999999999993E-2</v>
+        <v>0.151361</v>
       </c>
       <c r="AU6">
-        <v>9.7611000000000003E-2</v>
+        <v>0.15415899999999999</v>
       </c>
       <c r="AV6">
-        <v>8.9456999999999995E-2</v>
+        <v>0.141264</v>
       </c>
       <c r="AW6">
-        <v>0.13784099999999999</v>
+        <v>0.219504</v>
       </c>
       <c r="AX6">
-        <v>0.141539</v>
+        <v>0.22751299999999999</v>
       </c>
       <c r="AY6">
-        <v>0.151891</v>
+        <v>0.241564</v>
       </c>
       <c r="AZ6">
-        <v>0.16845399999999999</v>
+        <v>0.27090799999999998</v>
       </c>
       <c r="BA6">
-        <v>0.171236</v>
+        <v>0.26937800000000001</v>
       </c>
       <c r="BB6">
-        <v>0.14722199999999999</v>
+        <v>0.23697199999999999</v>
       </c>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.25">
@@ -4087,58 +4087,58 @@
         <v>17.726692</v>
       </c>
       <c r="AK7">
-        <v>7.1517999999999998E-2</v>
+        <v>0.11440500000000001</v>
       </c>
       <c r="AL7">
-        <v>7.5810000000000002E-2</v>
+        <v>0.12124600000000001</v>
       </c>
       <c r="AM7">
-        <v>7.8472E-2</v>
+        <v>0.12650900000000001</v>
       </c>
       <c r="AN7">
-        <v>8.2922999999999997E-2</v>
+        <v>0.13355900000000001</v>
       </c>
       <c r="AO7">
-        <v>8.0744999999999997E-2</v>
+        <v>0.12845999999999999</v>
       </c>
       <c r="AP7">
-        <v>7.6199000000000003E-2</v>
+        <v>0.121929</v>
       </c>
       <c r="AQ7">
-        <v>8.2432000000000005E-2</v>
+        <v>0.13159100000000001</v>
       </c>
       <c r="AR7">
-        <v>8.7951000000000001E-2</v>
+        <v>0.13733300000000001</v>
       </c>
       <c r="AS7">
-        <v>9.3870999999999996E-2</v>
+        <v>0.14909500000000001</v>
       </c>
       <c r="AT7">
-        <v>9.5069000000000001E-2</v>
+        <v>0.15327299999999999</v>
       </c>
       <c r="AU7">
-        <v>9.8656999999999995E-2</v>
+        <v>0.155499</v>
       </c>
       <c r="AV7">
-        <v>9.1847999999999999E-2</v>
+        <v>0.143897</v>
       </c>
       <c r="AW7">
-        <v>0.13991899999999999</v>
+        <v>0.22203300000000001</v>
       </c>
       <c r="AX7">
-        <v>0.14533199999999999</v>
+        <v>0.23462</v>
       </c>
       <c r="AY7">
-        <v>0.16644500000000001</v>
+        <v>0.25767400000000001</v>
       </c>
       <c r="AZ7">
-        <v>0.17080500000000001</v>
+        <v>0.27091799999999999</v>
       </c>
       <c r="BA7">
-        <v>0.17268700000000001</v>
+        <v>0.27208300000000002</v>
       </c>
       <c r="BB7">
-        <v>0.14927299999999999</v>
+        <v>0.24098</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.25">
@@ -4251,58 +4251,58 @@
         <v>23.005213000000001</v>
       </c>
       <c r="AK8">
-        <v>7.2133000000000003E-2</v>
+        <v>0.115383</v>
       </c>
       <c r="AL8">
-        <v>6.9857000000000002E-2</v>
+        <v>0.11178299999999999</v>
       </c>
       <c r="AM8">
-        <v>7.8038999999999997E-2</v>
+        <v>0.12439600000000001</v>
       </c>
       <c r="AN8">
-        <v>8.1504999999999994E-2</v>
+        <v>0.13059200000000001</v>
       </c>
       <c r="AO8">
-        <v>7.7670000000000003E-2</v>
+        <v>0.124013</v>
       </c>
       <c r="AP8">
-        <v>7.0630999999999999E-2</v>
+        <v>0.11294</v>
       </c>
       <c r="AQ8">
-        <v>7.9247999999999999E-2</v>
+        <v>0.12510599999999999</v>
       </c>
       <c r="AR8">
-        <v>7.9888000000000001E-2</v>
+        <v>0.12728200000000001</v>
       </c>
       <c r="AS8">
-        <v>8.5946999999999996E-2</v>
+        <v>0.13856599999999999</v>
       </c>
       <c r="AT8">
-        <v>9.3940999999999997E-2</v>
+        <v>0.15135199999999999</v>
       </c>
       <c r="AU8">
-        <v>9.1144000000000003E-2</v>
+        <v>0.14579800000000001</v>
       </c>
       <c r="AV8">
-        <v>8.1601000000000007E-2</v>
+        <v>0.13092799999999999</v>
       </c>
       <c r="AW8">
-        <v>0.131855</v>
+        <v>0.21127899999999999</v>
       </c>
       <c r="AX8">
-        <v>0.13262099999999999</v>
+        <v>0.21190999999999999</v>
       </c>
       <c r="AY8">
-        <v>0.15126500000000001</v>
+        <v>0.23682300000000001</v>
       </c>
       <c r="AZ8">
-        <v>0.16042899999999999</v>
+        <v>0.25933400000000001</v>
       </c>
       <c r="BA8">
-        <v>0.156418</v>
+        <v>0.24843399999999999</v>
       </c>
       <c r="BB8">
-        <v>0.14235100000000001</v>
+        <v>0.228551</v>
       </c>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.25">
@@ -4415,58 +4415,58 @@
         <v>20.354596000000001</v>
       </c>
       <c r="AK9">
-        <v>7.0872000000000004E-2</v>
+        <v>0.113396</v>
       </c>
       <c r="AL9">
-        <v>6.9149000000000002E-2</v>
+        <v>0.110662</v>
       </c>
       <c r="AM9">
-        <v>7.6484999999999997E-2</v>
+        <v>0.120909</v>
       </c>
       <c r="AN9">
-        <v>7.8112000000000001E-2</v>
+        <v>0.12325800000000001</v>
       </c>
       <c r="AO9">
-        <v>7.5894000000000003E-2</v>
+        <v>0.121984</v>
       </c>
       <c r="AP9">
-        <v>6.9455000000000003E-2</v>
+        <v>0.111219</v>
       </c>
       <c r="AQ9">
-        <v>7.8780000000000003E-2</v>
+        <v>0.12565699999999999</v>
       </c>
       <c r="AR9">
-        <v>7.7394000000000004E-2</v>
+        <v>0.124658</v>
       </c>
       <c r="AS9">
-        <v>7.6876E-2</v>
+        <v>0.12483900000000001</v>
       </c>
       <c r="AT9">
-        <v>8.9530999999999999E-2</v>
+        <v>0.14153499999999999</v>
       </c>
       <c r="AU9">
-        <v>8.9536000000000004E-2</v>
+        <v>0.14441899999999999</v>
       </c>
       <c r="AV9">
-        <v>7.9500000000000001E-2</v>
+        <v>0.12862799999999999</v>
       </c>
       <c r="AW9">
-        <v>0.12879199999999999</v>
+        <v>0.207483</v>
       </c>
       <c r="AX9">
-        <v>0.12955800000000001</v>
+        <v>0.20608599999999999</v>
       </c>
       <c r="AY9">
-        <v>0.13165099999999999</v>
+        <v>0.21943699999999999</v>
       </c>
       <c r="AZ9">
-        <v>0.14826</v>
+        <v>0.238013</v>
       </c>
       <c r="BA9">
-        <v>0.14990600000000001</v>
+        <v>0.24127799999999999</v>
       </c>
       <c r="BB9">
-        <v>0.13689499999999999</v>
+        <v>0.21801899999999999</v>
       </c>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.25">
@@ -4579,58 +4579,58 @@
         <v>15.896518</v>
       </c>
       <c r="AK10">
-        <v>6.9708000000000006E-2</v>
+        <v>0.11156000000000001</v>
       </c>
       <c r="AL10">
-        <v>6.9284999999999999E-2</v>
+        <v>0.11088000000000001</v>
       </c>
       <c r="AM10">
-        <v>7.6160000000000005E-2</v>
+        <v>0.120652</v>
       </c>
       <c r="AN10">
-        <v>7.6438000000000006E-2</v>
+        <v>0.119889</v>
       </c>
       <c r="AO10">
-        <v>7.3071999999999998E-2</v>
+        <v>0.119056</v>
       </c>
       <c r="AP10">
-        <v>6.8961999999999996E-2</v>
+        <v>0.110511</v>
       </c>
       <c r="AQ10">
-        <v>7.7350000000000002E-2</v>
+        <v>0.118816</v>
       </c>
       <c r="AR10">
-        <v>7.5597999999999999E-2</v>
+        <v>0.122762</v>
       </c>
       <c r="AS10">
-        <v>7.0599999999999996E-2</v>
+        <v>0.115533</v>
       </c>
       <c r="AT10">
-        <v>8.6583999999999994E-2</v>
+        <v>0.135188</v>
       </c>
       <c r="AU10">
-        <v>8.6812E-2</v>
+        <v>0.14268800000000001</v>
       </c>
       <c r="AV10">
-        <v>7.8212000000000004E-2</v>
+        <v>0.12739700000000001</v>
       </c>
       <c r="AW10">
-        <v>0.12678600000000001</v>
+        <v>0.205036</v>
       </c>
       <c r="AX10">
-        <v>0.12935199999999999</v>
+        <v>0.205819</v>
       </c>
       <c r="AY10">
-        <v>0.12506500000000001</v>
+        <v>0.211756</v>
       </c>
       <c r="AZ10">
-        <v>0.14164299999999999</v>
+        <v>0.22724900000000001</v>
       </c>
       <c r="BA10">
-        <v>0.14163600000000001</v>
+        <v>0.23289299999999999</v>
       </c>
       <c r="BB10">
-        <v>0.13222700000000001</v>
+        <v>0.208985</v>
       </c>
     </row>
     <row r="11" spans="1:54" x14ac:dyDescent="0.25">
@@ -4743,58 +4743,58 @@
         <v>15.740091</v>
       </c>
       <c r="AK11">
-        <v>6.9498000000000004E-2</v>
+        <v>0.111219</v>
       </c>
       <c r="AL11">
-        <v>7.0778999999999995E-2</v>
+        <v>0.113248</v>
       </c>
       <c r="AM11">
-        <v>7.7184000000000003E-2</v>
+        <v>0.124002</v>
       </c>
       <c r="AN11">
-        <v>7.8785999999999995E-2</v>
+        <v>0.12574399999999999</v>
       </c>
       <c r="AO11">
-        <v>7.5534000000000004E-2</v>
+        <v>0.12167699999999999</v>
       </c>
       <c r="AP11">
-        <v>6.9928000000000004E-2</v>
+        <v>0.11194800000000001</v>
       </c>
       <c r="AQ11">
-        <v>7.8075000000000006E-2</v>
+        <v>0.12467</v>
       </c>
       <c r="AR11">
-        <v>7.7048000000000005E-2</v>
+        <v>0.12399499999999999</v>
       </c>
       <c r="AS11">
-        <v>7.4634000000000006E-2</v>
+        <v>0.121763</v>
       </c>
       <c r="AT11">
-        <v>8.8255E-2</v>
+        <v>0.13980899999999999</v>
       </c>
       <c r="AU11">
-        <v>8.9373999999999995E-2</v>
+        <v>0.145005</v>
       </c>
       <c r="AV11">
-        <v>8.2869999999999999E-2</v>
+        <v>0.13230600000000001</v>
       </c>
       <c r="AW11">
-        <v>0.12758700000000001</v>
+        <v>0.20605999999999999</v>
       </c>
       <c r="AX11">
-        <v>0.130023</v>
+        <v>0.20704800000000001</v>
       </c>
       <c r="AY11">
-        <v>0.138515</v>
+        <v>0.219442</v>
       </c>
       <c r="AZ11">
-        <v>0.148177</v>
+        <v>0.241559</v>
       </c>
       <c r="BA11">
-        <v>0.146116</v>
+        <v>0.23749500000000001</v>
       </c>
       <c r="BB11">
-        <v>0.13400200000000001</v>
+        <v>0.21265899999999999</v>
       </c>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.25">
@@ -4907,58 +4907,58 @@
         <v>17.03237</v>
       </c>
       <c r="AK12">
-        <v>6.9065000000000001E-2</v>
+        <v>0.11053399999999999</v>
       </c>
       <c r="AL12">
-        <v>7.084E-2</v>
+        <v>0.113358</v>
       </c>
       <c r="AM12">
-        <v>7.5259999999999994E-2</v>
+        <v>0.11895799999999999</v>
       </c>
       <c r="AN12">
-        <v>7.8242999999999993E-2</v>
+        <v>0.12418999999999999</v>
       </c>
       <c r="AO12">
-        <v>7.5938000000000005E-2</v>
+        <v>0.122599</v>
       </c>
       <c r="AP12">
-        <v>7.0670999999999998E-2</v>
+        <v>0.11312</v>
       </c>
       <c r="AQ12">
-        <v>7.8010999999999997E-2</v>
+        <v>0.124111</v>
       </c>
       <c r="AR12">
-        <v>7.5314000000000006E-2</v>
+        <v>0.122833</v>
       </c>
       <c r="AS12">
-        <v>7.5037000000000006E-2</v>
+        <v>0.122319</v>
       </c>
       <c r="AT12">
-        <v>8.9149000000000006E-2</v>
+        <v>0.14147899999999999</v>
       </c>
       <c r="AU12">
-        <v>9.1175999999999993E-2</v>
+        <v>0.14744599999999999</v>
       </c>
       <c r="AV12">
-        <v>8.2644999999999996E-2</v>
+        <v>0.132574</v>
       </c>
       <c r="AW12">
-        <v>0.12945799999999999</v>
+        <v>0.20859900000000001</v>
       </c>
       <c r="AX12">
-        <v>0.12914700000000001</v>
+        <v>0.20482900000000001</v>
       </c>
       <c r="AY12">
-        <v>0.13130800000000001</v>
+        <v>0.21538599999999999</v>
       </c>
       <c r="AZ12">
-        <v>0.150115</v>
+        <v>0.24358099999999999</v>
       </c>
       <c r="BA12">
-        <v>0.148836</v>
+        <v>0.24177000000000001</v>
       </c>
       <c r="BB12">
-        <v>0.136737</v>
+        <v>0.217863</v>
       </c>
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.25">
@@ -5071,58 +5071,58 @@
         <v>17.617819000000001</v>
       </c>
       <c r="AK13">
-        <v>6.8987999999999994E-2</v>
+        <v>0.110411</v>
       </c>
       <c r="AL13">
-        <v>7.0666000000000007E-2</v>
+        <v>0.11310099999999999</v>
       </c>
       <c r="AM13">
-        <v>7.4146000000000004E-2</v>
+        <v>0.115607</v>
       </c>
       <c r="AN13">
-        <v>7.8132999999999994E-2</v>
+        <v>0.12329900000000001</v>
       </c>
       <c r="AO13">
-        <v>7.6747999999999997E-2</v>
+        <v>0.124038</v>
       </c>
       <c r="AP13">
-        <v>7.1247000000000005E-2</v>
+        <v>0.11409900000000001</v>
       </c>
       <c r="AQ13">
-        <v>7.8089000000000006E-2</v>
+        <v>0.12317500000000001</v>
       </c>
       <c r="AR13">
-        <v>7.5521000000000005E-2</v>
+        <v>0.123846</v>
       </c>
       <c r="AS13">
-        <v>7.5392000000000001E-2</v>
+        <v>0.122627</v>
       </c>
       <c r="AT13">
-        <v>8.9934E-2</v>
+        <v>0.142372</v>
       </c>
       <c r="AU13">
-        <v>9.2077000000000006E-2</v>
+        <v>0.14962900000000001</v>
       </c>
       <c r="AV13">
-        <v>8.2966999999999999E-2</v>
+        <v>0.13339799999999999</v>
       </c>
       <c r="AW13">
-        <v>0.13158400000000001</v>
+        <v>0.211585</v>
       </c>
       <c r="AX13">
-        <v>0.13036200000000001</v>
+        <v>0.20649300000000001</v>
       </c>
       <c r="AY13">
-        <v>0.12781300000000001</v>
+        <v>0.21632599999999999</v>
       </c>
       <c r="AZ13">
-        <v>0.15104300000000001</v>
+        <v>0.24166199999999999</v>
       </c>
       <c r="BA13">
-        <v>0.15452099999999999</v>
+        <v>0.249582</v>
       </c>
       <c r="BB13">
-        <v>0.139597</v>
+        <v>0.223163</v>
       </c>
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.25">
@@ -5235,58 +5235,58 @@
         <v>18.937646999999998</v>
       </c>
       <c r="AK14">
-        <v>6.9513000000000005E-2</v>
+        <v>0.111239</v>
       </c>
       <c r="AL14">
-        <v>7.2923000000000002E-2</v>
+        <v>0.116684</v>
       </c>
       <c r="AM14">
-        <v>7.7067999999999998E-2</v>
+        <v>0.12245399999999999</v>
       </c>
       <c r="AN14">
-        <v>8.1323999999999994E-2</v>
+        <v>0.12987000000000001</v>
       </c>
       <c r="AO14">
-        <v>8.0278000000000002E-2</v>
+        <v>0.12820300000000001</v>
       </c>
       <c r="AP14">
-        <v>7.1901999999999994E-2</v>
+        <v>0.11522</v>
       </c>
       <c r="AQ14">
-        <v>7.9059000000000004E-2</v>
+        <v>0.124836</v>
       </c>
       <c r="AR14">
-        <v>7.9796000000000006E-2</v>
+        <v>0.12883800000000001</v>
       </c>
       <c r="AS14">
-        <v>8.5130999999999998E-2</v>
+        <v>0.13681399999999999</v>
       </c>
       <c r="AT14">
-        <v>9.2809000000000003E-2</v>
+        <v>0.14822299999999999</v>
       </c>
       <c r="AU14">
-        <v>9.7741999999999996E-2</v>
+        <v>0.154922</v>
       </c>
       <c r="AV14">
-        <v>8.3500000000000005E-2</v>
+        <v>0.134441</v>
       </c>
       <c r="AW14">
-        <v>0.13575200000000001</v>
+        <v>0.21692900000000001</v>
       </c>
       <c r="AX14">
-        <v>0.13636799999999999</v>
+        <v>0.217584</v>
       </c>
       <c r="AY14">
-        <v>0.145596</v>
+        <v>0.235705</v>
       </c>
       <c r="AZ14">
-        <v>0.161797</v>
+        <v>0.25827600000000001</v>
       </c>
       <c r="BA14">
-        <v>0.16458</v>
+        <v>0.26159100000000002</v>
       </c>
       <c r="BB14">
-        <v>0.14014299999999999</v>
+        <v>0.223806</v>
       </c>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
@@ -5399,58 +5399,58 @@
         <v>18.406137000000001</v>
       </c>
       <c r="AK15">
-        <v>7.0349999999999996E-2</v>
+        <v>0.112555</v>
       </c>
       <c r="AL15">
-        <v>7.6379000000000002E-2</v>
+        <v>0.122156</v>
       </c>
       <c r="AM15">
-        <v>8.0369999999999997E-2</v>
+        <v>0.13025400000000001</v>
       </c>
       <c r="AN15">
-        <v>8.4527000000000005E-2</v>
+        <v>0.13663600000000001</v>
       </c>
       <c r="AO15">
-        <v>8.2265000000000005E-2</v>
+        <v>0.13060099999999999</v>
       </c>
       <c r="AP15">
-        <v>7.3166999999999996E-2</v>
+        <v>0.117205</v>
       </c>
       <c r="AQ15">
-        <v>8.0738000000000004E-2</v>
+        <v>0.130213</v>
       </c>
       <c r="AR15">
-        <v>8.6609000000000005E-2</v>
+        <v>0.13583600000000001</v>
       </c>
       <c r="AS15">
-        <v>9.6422999999999995E-2</v>
+        <v>0.15293999999999999</v>
       </c>
       <c r="AT15">
-        <v>9.5754000000000006E-2</v>
+        <v>0.154473</v>
       </c>
       <c r="AU15">
-        <v>0.10292900000000001</v>
+        <v>0.15926899999999999</v>
       </c>
       <c r="AV15">
-        <v>8.5655999999999996E-2</v>
+        <v>0.136959</v>
       </c>
       <c r="AW15">
-        <v>0.139649</v>
+        <v>0.22171099999999999</v>
       </c>
       <c r="AX15">
-        <v>0.143653</v>
+        <v>0.23146700000000001</v>
       </c>
       <c r="AY15">
-        <v>0.16850899999999999</v>
+        <v>0.25864900000000002</v>
       </c>
       <c r="AZ15">
-        <v>0.17330200000000001</v>
+        <v>0.27620800000000001</v>
       </c>
       <c r="BA15">
-        <v>0.16969999999999999</v>
+        <v>0.26812399999999997</v>
       </c>
       <c r="BB15">
-        <v>0.14141500000000001</v>
+        <v>0.2261</v>
       </c>
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.25">
@@ -5563,58 +5563,58 @@
         <v>19.762678999999999</v>
       </c>
       <c r="AK16">
-        <v>7.2158E-2</v>
+        <v>0.115423</v>
       </c>
       <c r="AL16">
-        <v>7.1214E-2</v>
+        <v>0.113931</v>
       </c>
       <c r="AM16">
-        <v>8.3379999999999996E-2</v>
+        <v>0.13580200000000001</v>
       </c>
       <c r="AN16">
-        <v>8.7858000000000006E-2</v>
+        <v>0.14335600000000001</v>
       </c>
       <c r="AO16">
-        <v>7.9950999999999994E-2</v>
+        <v>0.12690199999999999</v>
       </c>
       <c r="AP16">
-        <v>7.1410000000000001E-2</v>
+        <v>0.114033</v>
       </c>
       <c r="AQ16">
-        <v>8.0014000000000002E-2</v>
+        <v>0.12940599999999999</v>
       </c>
       <c r="AR16">
-        <v>8.0139000000000002E-2</v>
+        <v>0.127609</v>
       </c>
       <c r="AS16">
-        <v>0.102198</v>
+        <v>0.161192</v>
       </c>
       <c r="AT16">
-        <v>9.8549999999999999E-2</v>
+        <v>0.160273</v>
       </c>
       <c r="AU16">
-        <v>9.2240000000000003E-2</v>
+        <v>0.147033</v>
       </c>
       <c r="AV16">
-        <v>8.2909999999999998E-2</v>
+        <v>0.13236899999999999</v>
       </c>
       <c r="AW16">
-        <v>0.13550200000000001</v>
+        <v>0.215808</v>
       </c>
       <c r="AX16">
-        <v>0.133546</v>
+        <v>0.21341399999999999</v>
       </c>
       <c r="AY16">
-        <v>0.16498699999999999</v>
+        <v>0.25703199999999998</v>
       </c>
       <c r="AZ16">
-        <v>0.17478299999999999</v>
+        <v>0.27930300000000002</v>
       </c>
       <c r="BA16">
-        <v>0.15762599999999999</v>
+        <v>0.25030000000000002</v>
       </c>
       <c r="BB16">
-        <v>0.14204800000000001</v>
+        <v>0.22790299999999999</v>
       </c>
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.25">
@@ -5727,58 +5727,58 @@
         <v>19.328526</v>
       </c>
       <c r="AK17">
-        <v>7.1388999999999994E-2</v>
+        <v>0.114209</v>
       </c>
       <c r="AL17">
-        <v>7.0415000000000005E-2</v>
+        <v>0.11266900000000001</v>
       </c>
       <c r="AM17">
-        <v>8.2225000000000006E-2</v>
+        <v>0.13314000000000001</v>
       </c>
       <c r="AN17">
-        <v>8.6953000000000003E-2</v>
+        <v>0.141649</v>
       </c>
       <c r="AO17">
-        <v>7.8611E-2</v>
+        <v>0.125469</v>
       </c>
       <c r="AP17">
-        <v>6.9830000000000003E-2</v>
+        <v>0.111719</v>
       </c>
       <c r="AQ17">
-        <v>7.9259999999999997E-2</v>
+        <v>0.12822900000000001</v>
       </c>
       <c r="AR17">
-        <v>7.8048999999999993E-2</v>
+        <v>0.12537799999999999</v>
       </c>
       <c r="AS17">
-        <v>9.9186999999999997E-2</v>
+        <v>0.15726799999999999</v>
       </c>
       <c r="AT17">
-        <v>9.5904000000000003E-2</v>
+        <v>0.15479000000000001</v>
       </c>
       <c r="AU17">
-        <v>9.0690999999999994E-2</v>
+        <v>0.145733</v>
       </c>
       <c r="AV17">
-        <v>8.0457000000000001E-2</v>
+        <v>0.12970599999999999</v>
       </c>
       <c r="AW17">
-        <v>0.132969</v>
+        <v>0.212697</v>
       </c>
       <c r="AX17">
-        <v>0.13136999999999999</v>
+        <v>0.20932799999999999</v>
       </c>
       <c r="AY17">
-        <v>0.159719</v>
+        <v>0.24993199999999999</v>
       </c>
       <c r="AZ17">
-        <v>0.17095099999999999</v>
+        <v>0.27575699999999997</v>
       </c>
       <c r="BA17">
-        <v>0.153895</v>
+        <v>0.245945</v>
       </c>
       <c r="BB17">
-        <v>0.137517</v>
+        <v>0.21923500000000001</v>
       </c>
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.25">
@@ -5891,58 +5891,58 @@
         <v>17.066497999999999</v>
       </c>
       <c r="AK18">
-        <v>7.0600999999999997E-2</v>
+        <v>0.11296100000000001</v>
       </c>
       <c r="AL18">
-        <v>6.9936999999999999E-2</v>
+        <v>0.111919</v>
       </c>
       <c r="AM18">
-        <v>7.9717999999999997E-2</v>
+        <v>0.12690199999999999</v>
       </c>
       <c r="AN18">
-        <v>8.3199999999999996E-2</v>
+        <v>0.13339100000000001</v>
       </c>
       <c r="AO18">
-        <v>7.6297000000000004E-2</v>
+        <v>0.123219</v>
       </c>
       <c r="AP18">
-        <v>6.8659999999999999E-2</v>
+        <v>0.110015</v>
       </c>
       <c r="AQ18">
-        <v>7.8030000000000002E-2</v>
+        <v>0.123797</v>
       </c>
       <c r="AR18">
-        <v>7.5858999999999996E-2</v>
+        <v>0.123239</v>
       </c>
       <c r="AS18">
-        <v>8.7135000000000004E-2</v>
+        <v>0.13927300000000001</v>
       </c>
       <c r="AT18">
-        <v>9.1610999999999998E-2</v>
+        <v>0.145061</v>
       </c>
       <c r="AU18">
-        <v>8.7503999999999998E-2</v>
+        <v>0.143729</v>
       </c>
       <c r="AV18">
-        <v>7.8890000000000002E-2</v>
+        <v>0.128134</v>
       </c>
       <c r="AW18">
-        <v>0.131469</v>
+        <v>0.210845</v>
       </c>
       <c r="AX18">
-        <v>0.13003200000000001</v>
+        <v>0.20666699999999999</v>
       </c>
       <c r="AY18">
-        <v>0.14483199999999999</v>
+        <v>0.236898</v>
       </c>
       <c r="AZ18">
-        <v>0.15845999999999999</v>
+        <v>0.253193</v>
       </c>
       <c r="BA18">
-        <v>0.14848</v>
+        <v>0.240371</v>
       </c>
       <c r="BB18">
-        <v>0.13437499999999999</v>
+        <v>0.21329999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.25">
@@ -6055,58 +6055,58 @@
         <v>16.071134000000001</v>
       </c>
       <c r="AK19">
-        <v>7.0241999999999999E-2</v>
+        <v>0.112388</v>
       </c>
       <c r="AL19">
-        <v>7.1936E-2</v>
+        <v>0.11508699999999999</v>
       </c>
       <c r="AM19">
-        <v>8.0486000000000002E-2</v>
+        <v>0.12989700000000001</v>
       </c>
       <c r="AN19">
-        <v>8.2425999999999999E-2</v>
+        <v>0.13228300000000001</v>
       </c>
       <c r="AO19">
-        <v>7.7595999999999998E-2</v>
+        <v>0.124751</v>
       </c>
       <c r="AP19">
-        <v>6.8611000000000005E-2</v>
+        <v>0.10996599999999999</v>
       </c>
       <c r="AQ19">
-        <v>7.8164999999999998E-2</v>
+        <v>0.126807</v>
       </c>
       <c r="AR19">
-        <v>7.8057000000000001E-2</v>
+        <v>0.12520600000000001</v>
       </c>
       <c r="AS19">
-        <v>8.9630000000000001E-2</v>
+        <v>0.14400499999999999</v>
       </c>
       <c r="AT19">
-        <v>9.1676999999999995E-2</v>
+        <v>0.14608199999999999</v>
       </c>
       <c r="AU19">
-        <v>8.9360999999999996E-2</v>
+        <v>0.14546100000000001</v>
       </c>
       <c r="AV19">
-        <v>7.9866999999999994E-2</v>
+        <v>0.129306</v>
       </c>
       <c r="AW19">
-        <v>0.13147400000000001</v>
+        <v>0.21087</v>
       </c>
       <c r="AX19">
-        <v>0.13209299999999999</v>
+        <v>0.210676</v>
       </c>
       <c r="AY19">
-        <v>0.15592500000000001</v>
+        <v>0.24071300000000001</v>
       </c>
       <c r="AZ19">
-        <v>0.15839300000000001</v>
+        <v>0.25676599999999999</v>
       </c>
       <c r="BA19">
-        <v>0.150815</v>
+        <v>0.242699</v>
       </c>
       <c r="BB19">
-        <v>0.13419300000000001</v>
+        <v>0.21308299999999999</v>
       </c>
     </row>
     <row r="20" spans="1:54" x14ac:dyDescent="0.25">
@@ -6219,58 +6219,58 @@
         <v>16.553794</v>
       </c>
       <c r="AK20">
-        <v>6.9749000000000005E-2</v>
+        <v>0.111607</v>
       </c>
       <c r="AL20">
-        <v>7.2469000000000006E-2</v>
+        <v>0.115941</v>
       </c>
       <c r="AM20">
-        <v>7.7717999999999995E-2</v>
+        <v>0.122942</v>
       </c>
       <c r="AN20">
-        <v>7.9934000000000005E-2</v>
+        <v>0.12668499999999999</v>
       </c>
       <c r="AO20">
-        <v>7.7641000000000002E-2</v>
+        <v>0.125274</v>
       </c>
       <c r="AP20">
-        <v>6.9517999999999996E-2</v>
+        <v>0.111344</v>
       </c>
       <c r="AQ20">
-        <v>7.7979999999999994E-2</v>
+        <v>0.12574199999999999</v>
       </c>
       <c r="AR20">
-        <v>7.7019000000000004E-2</v>
+        <v>0.124671</v>
       </c>
       <c r="AS20">
-        <v>8.1864999999999993E-2</v>
+        <v>0.132442</v>
       </c>
       <c r="AT20">
-        <v>9.1289999999999996E-2</v>
+        <v>0.145126</v>
       </c>
       <c r="AU20">
-        <v>9.0106000000000006E-2</v>
+        <v>0.14707300000000001</v>
       </c>
       <c r="AV20">
-        <v>8.1460000000000005E-2</v>
+        <v>0.131275</v>
       </c>
       <c r="AW20">
-        <v>0.13162699999999999</v>
+        <v>0.21129200000000001</v>
       </c>
       <c r="AX20">
-        <v>0.131352</v>
+        <v>0.20875099999999999</v>
       </c>
       <c r="AY20">
-        <v>0.14110700000000001</v>
+        <v>0.22902700000000001</v>
       </c>
       <c r="AZ20">
-        <v>0.15392</v>
+        <v>0.24790599999999999</v>
       </c>
       <c r="BA20">
-        <v>0.15021300000000001</v>
+        <v>0.24331700000000001</v>
       </c>
       <c r="BB20">
-        <v>0.137096</v>
+        <v>0.21876999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.25">
@@ -6383,58 +6383,58 @@
         <v>16.401710999999999</v>
       </c>
       <c r="AK21">
-        <v>6.9381999999999999E-2</v>
+        <v>0.111028</v>
       </c>
       <c r="AL21">
-        <v>7.2111999999999996E-2</v>
+        <v>0.115395</v>
       </c>
       <c r="AM21">
-        <v>7.7149999999999996E-2</v>
+        <v>0.121365</v>
       </c>
       <c r="AN21">
-        <v>8.0091999999999997E-2</v>
+        <v>0.126748</v>
       </c>
       <c r="AO21">
-        <v>8.0315999999999999E-2</v>
+        <v>0.12856300000000001</v>
       </c>
       <c r="AP21">
-        <v>7.0261000000000004E-2</v>
+        <v>0.11255900000000001</v>
       </c>
       <c r="AQ21">
-        <v>7.8062000000000006E-2</v>
+        <v>0.124238</v>
       </c>
       <c r="AR21">
-        <v>7.7154E-2</v>
+        <v>0.12564</v>
       </c>
       <c r="AS21">
-        <v>7.9372999999999999E-2</v>
+        <v>0.12861900000000001</v>
       </c>
       <c r="AT21">
-        <v>9.2284000000000005E-2</v>
+        <v>0.14687800000000001</v>
       </c>
       <c r="AU21">
-        <v>9.3684000000000003E-2</v>
+        <v>0.151083</v>
       </c>
       <c r="AV21">
-        <v>8.2608000000000001E-2</v>
+        <v>0.13291900000000001</v>
       </c>
       <c r="AW21">
-        <v>0.13366800000000001</v>
+        <v>0.21410399999999999</v>
       </c>
       <c r="AX21">
-        <v>0.132942</v>
+        <v>0.21118200000000001</v>
       </c>
       <c r="AY21">
-        <v>0.13786599999999999</v>
+        <v>0.22789799999999999</v>
       </c>
       <c r="AZ21">
-        <v>0.15651200000000001</v>
+        <v>0.25085400000000002</v>
       </c>
       <c r="BA21">
-        <v>0.15675800000000001</v>
+        <v>0.25156800000000001</v>
       </c>
       <c r="BB21">
-        <v>0.141765</v>
+        <v>0.22786500000000001</v>
       </c>
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.25">
@@ -6547,58 +6547,58 @@
         <v>22.713732</v>
       </c>
       <c r="AK22">
-        <v>6.9669999999999996E-2</v>
+        <v>0.11148</v>
       </c>
       <c r="AL22">
-        <v>7.5326000000000004E-2</v>
+        <v>0.120488</v>
       </c>
       <c r="AM22">
-        <v>8.0346000000000001E-2</v>
+        <v>0.12932399999999999</v>
       </c>
       <c r="AN22">
-        <v>8.4292000000000006E-2</v>
+        <v>0.135967</v>
       </c>
       <c r="AO22">
-        <v>8.2901000000000002E-2</v>
+        <v>0.131635</v>
       </c>
       <c r="AP22">
-        <v>7.1365999999999999E-2</v>
+        <v>0.11430999999999999</v>
       </c>
       <c r="AQ22">
-        <v>7.9242999999999994E-2</v>
+        <v>0.12720699999999999</v>
       </c>
       <c r="AR22">
-        <v>8.2877999999999993E-2</v>
+        <v>0.13175500000000001</v>
       </c>
       <c r="AS22">
-        <v>8.6313000000000001E-2</v>
+        <v>0.138572</v>
       </c>
       <c r="AT22">
-        <v>9.5258999999999996E-2</v>
+        <v>0.15329799999999999</v>
       </c>
       <c r="AU22">
-        <v>0.100011</v>
+        <v>0.15675800000000001</v>
       </c>
       <c r="AV22">
-        <v>8.3193000000000003E-2</v>
+        <v>0.13397600000000001</v>
       </c>
       <c r="AW22">
-        <v>0.136238</v>
+        <v>0.21751100000000001</v>
       </c>
       <c r="AX22">
-        <v>0.13883599999999999</v>
+        <v>0.22218499999999999</v>
       </c>
       <c r="AY22">
-        <v>0.14773500000000001</v>
+        <v>0.239784</v>
       </c>
       <c r="AZ22">
-        <v>0.166322</v>
+        <v>0.26612400000000003</v>
       </c>
       <c r="BA22">
-        <v>0.165243</v>
+        <v>0.261598</v>
       </c>
       <c r="BB22">
-        <v>0.14052400000000001</v>
+        <v>0.22499</v>
       </c>
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.25">
@@ -6711,58 +6711,58 @@
         <v>21.137855999999999</v>
       </c>
       <c r="AK23">
-        <v>7.0188E-2</v>
+        <v>0.112293</v>
       </c>
       <c r="AL23">
-        <v>7.7546000000000004E-2</v>
+        <v>0.124005</v>
       </c>
       <c r="AM23">
-        <v>8.2225999999999994E-2</v>
+        <v>0.13356599999999999</v>
       </c>
       <c r="AN23">
-        <v>8.6610999999999994E-2</v>
+        <v>0.14080200000000001</v>
       </c>
       <c r="AO23">
-        <v>8.3468000000000001E-2</v>
+        <v>0.13244800000000001</v>
       </c>
       <c r="AP23">
-        <v>7.3284000000000002E-2</v>
+        <v>0.117215</v>
       </c>
       <c r="AQ23">
-        <v>8.0300999999999997E-2</v>
+        <v>0.128828</v>
       </c>
       <c r="AR23">
-        <v>8.7400000000000005E-2</v>
+        <v>0.13661799999999999</v>
       </c>
       <c r="AS23">
-        <v>9.4832E-2</v>
+        <v>0.15041199999999999</v>
       </c>
       <c r="AT23">
-        <v>9.6605999999999997E-2</v>
+        <v>0.15564800000000001</v>
       </c>
       <c r="AU23">
-        <v>0.105528</v>
+        <v>0.16123799999999999</v>
       </c>
       <c r="AV23">
-        <v>8.5708999999999994E-2</v>
+        <v>0.13683899999999999</v>
       </c>
       <c r="AW23">
-        <v>0.13911799999999999</v>
+        <v>0.22106899999999999</v>
       </c>
       <c r="AX23">
-        <v>0.14351</v>
+        <v>0.23089000000000001</v>
       </c>
       <c r="AY23">
-        <v>0.161466</v>
+        <v>0.25526399999999999</v>
       </c>
       <c r="AZ23">
-        <v>0.17441100000000001</v>
+        <v>0.27682499999999999</v>
       </c>
       <c r="BA23">
-        <v>0.16565199999999999</v>
+        <v>0.26348500000000002</v>
       </c>
       <c r="BB23">
-        <v>0.14070199999999999</v>
+        <v>0.22512699999999999</v>
       </c>
     </row>
     <row r="24" spans="1:54" x14ac:dyDescent="0.25">
@@ -6875,58 +6875,58 @@
         <v>19.331265999999999</v>
       </c>
       <c r="AK24">
-        <v>7.1960999999999997E-2</v>
+        <v>0.115108</v>
       </c>
       <c r="AL24">
-        <v>7.0789000000000005E-2</v>
+        <v>0.113271</v>
       </c>
       <c r="AM24">
-        <v>8.7423000000000001E-2</v>
+        <v>0.142933</v>
       </c>
       <c r="AN24">
-        <v>9.0812000000000004E-2</v>
+        <v>0.148148</v>
       </c>
       <c r="AO24">
-        <v>8.0452999999999997E-2</v>
+        <v>0.12808900000000001</v>
       </c>
       <c r="AP24">
-        <v>7.1909000000000001E-2</v>
+        <v>0.114866</v>
       </c>
       <c r="AQ24">
-        <v>8.0499000000000001E-2</v>
+        <v>0.129275</v>
       </c>
       <c r="AR24">
-        <v>8.0673999999999996E-2</v>
+        <v>0.12873200000000001</v>
       </c>
       <c r="AS24">
-        <v>0.113702</v>
+        <v>0.17749400000000001</v>
       </c>
       <c r="AT24">
-        <v>0.103411</v>
+        <v>0.168771</v>
       </c>
       <c r="AU24">
-        <v>9.3585000000000002E-2</v>
+        <v>0.14899100000000001</v>
       </c>
       <c r="AV24">
-        <v>8.4631999999999999E-2</v>
+        <v>0.13483999999999999</v>
       </c>
       <c r="AW24">
-        <v>0.137519</v>
+        <v>0.21874499999999999</v>
       </c>
       <c r="AX24">
-        <v>0.13791900000000001</v>
+        <v>0.22101499999999999</v>
       </c>
       <c r="AY24">
-        <v>0.17732300000000001</v>
+        <v>0.27887800000000001</v>
       </c>
       <c r="AZ24">
-        <v>0.181893</v>
+        <v>0.28669099999999997</v>
       </c>
       <c r="BA24">
-        <v>0.158863</v>
+        <v>0.25313000000000002</v>
       </c>
       <c r="BB24">
-        <v>0.14455599999999999</v>
+        <v>0.23216200000000001</v>
       </c>
     </row>
     <row r="25" spans="1:54" x14ac:dyDescent="0.25">
@@ -7039,58 +7039,58 @@
         <v>21.333708000000001</v>
       </c>
       <c r="AK25">
-        <v>7.1337999999999999E-2</v>
+        <v>0.11412600000000001</v>
       </c>
       <c r="AL25">
-        <v>7.0687E-2</v>
+        <v>0.113111</v>
       </c>
       <c r="AM25">
-        <v>8.7222999999999995E-2</v>
+        <v>0.142293</v>
       </c>
       <c r="AN25">
-        <v>9.0608999999999995E-2</v>
+        <v>0.14772199999999999</v>
       </c>
       <c r="AO25">
-        <v>8.0819000000000002E-2</v>
+        <v>0.12864300000000001</v>
       </c>
       <c r="AP25">
-        <v>7.1583999999999995E-2</v>
+        <v>0.11438</v>
       </c>
       <c r="AQ25">
-        <v>7.9982999999999999E-2</v>
+        <v>0.12963</v>
       </c>
       <c r="AR25">
-        <v>7.9689999999999997E-2</v>
+        <v>0.127724</v>
       </c>
       <c r="AS25">
-        <v>0.123974</v>
+        <v>0.19450899999999999</v>
       </c>
       <c r="AT25">
-        <v>0.101858</v>
+        <v>0.16553000000000001</v>
       </c>
       <c r="AU25">
-        <v>9.3803999999999998E-2</v>
+        <v>0.149113</v>
       </c>
       <c r="AV25">
-        <v>8.4460999999999994E-2</v>
+        <v>0.134607</v>
       </c>
       <c r="AW25">
-        <v>0.136601</v>
+        <v>0.21762899999999999</v>
       </c>
       <c r="AX25">
-        <v>0.13746</v>
+        <v>0.22006999999999999</v>
       </c>
       <c r="AY25">
-        <v>0.18228</v>
+        <v>0.28142699999999998</v>
       </c>
       <c r="AZ25">
-        <v>0.18273800000000001</v>
+        <v>0.29151300000000002</v>
       </c>
       <c r="BA25">
-        <v>0.15953000000000001</v>
+        <v>0.253552</v>
       </c>
       <c r="BB25">
-        <v>0.143924</v>
+        <v>0.231131</v>
       </c>
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.25">
@@ -7203,58 +7203,58 @@
         <v>22.850348</v>
       </c>
       <c r="AK26">
-        <v>7.0653999999999995E-2</v>
+        <v>0.113043</v>
       </c>
       <c r="AL26">
-        <v>7.0903999999999995E-2</v>
+        <v>0.11346100000000001</v>
       </c>
       <c r="AM26">
-        <v>8.4359000000000003E-2</v>
+        <v>0.13522200000000001</v>
       </c>
       <c r="AN26">
-        <v>8.7467000000000003E-2</v>
+        <v>0.14108999999999999</v>
       </c>
       <c r="AO26">
-        <v>8.0730999999999997E-2</v>
+        <v>0.128886</v>
       </c>
       <c r="AP26">
-        <v>7.1407999999999999E-2</v>
+        <v>0.114117</v>
       </c>
       <c r="AQ26">
-        <v>7.9033000000000006E-2</v>
+        <v>0.128305</v>
       </c>
       <c r="AR26">
-        <v>7.8643000000000005E-2</v>
+        <v>0.126827</v>
       </c>
       <c r="AS26">
-        <v>0.111425</v>
+        <v>0.17594000000000001</v>
       </c>
       <c r="AT26">
-        <v>9.7307000000000005E-2</v>
+        <v>0.155359</v>
       </c>
       <c r="AU26">
-        <v>9.3146000000000007E-2</v>
+        <v>0.14882500000000001</v>
       </c>
       <c r="AV26">
-        <v>8.3602999999999997E-2</v>
+        <v>0.133766</v>
       </c>
       <c r="AW26">
-        <v>0.13389400000000001</v>
+        <v>0.21435899999999999</v>
       </c>
       <c r="AX26">
-        <v>0.13655900000000001</v>
+        <v>0.21806600000000001</v>
       </c>
       <c r="AY26">
-        <v>0.16989499999999999</v>
+        <v>0.26989400000000002</v>
       </c>
       <c r="AZ26">
-        <v>0.17569899999999999</v>
+        <v>0.28073399999999998</v>
       </c>
       <c r="BA26">
-        <v>0.158775</v>
+        <v>0.25267899999999999</v>
       </c>
       <c r="BB26">
-        <v>0.14176900000000001</v>
+        <v>0.227182</v>
       </c>
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.25">
@@ -7367,58 +7367,58 @@
         <v>19.550591000000001</v>
       </c>
       <c r="AK27">
-        <v>7.0721999999999993E-2</v>
+        <v>0.11314200000000001</v>
       </c>
       <c r="AL27">
-        <v>7.1775000000000005E-2</v>
+        <v>0.114847</v>
       </c>
       <c r="AM27">
-        <v>8.2455000000000001E-2</v>
+        <v>0.13101199999999999</v>
       </c>
       <c r="AN27">
-        <v>8.4175E-2</v>
+        <v>0.13425100000000001</v>
       </c>
       <c r="AO27">
-        <v>8.2424999999999998E-2</v>
+        <v>0.131054</v>
       </c>
       <c r="AP27">
-        <v>7.1427000000000004E-2</v>
+        <v>0.11415400000000001</v>
       </c>
       <c r="AQ27">
-        <v>7.8148999999999996E-2</v>
+        <v>0.12576200000000001</v>
       </c>
       <c r="AR27">
-        <v>7.9945000000000002E-2</v>
+        <v>0.128191</v>
       </c>
       <c r="AS27">
-        <v>9.2970999999999998E-2</v>
+        <v>0.14835899999999999</v>
       </c>
       <c r="AT27">
-        <v>9.4987000000000002E-2</v>
+        <v>0.150759</v>
       </c>
       <c r="AU27">
-        <v>9.3265000000000001E-2</v>
+        <v>0.149311</v>
       </c>
       <c r="AV27">
-        <v>8.3585000000000007E-2</v>
+        <v>0.13388</v>
       </c>
       <c r="AW27">
-        <v>0.13297900000000001</v>
+        <v>0.21323800000000001</v>
       </c>
       <c r="AX27">
-        <v>0.13760700000000001</v>
+        <v>0.219861</v>
       </c>
       <c r="AY27">
-        <v>0.15972600000000001</v>
+        <v>0.25867499999999999</v>
       </c>
       <c r="AZ27">
-        <v>0.16591600000000001</v>
+        <v>0.26383099999999998</v>
       </c>
       <c r="BA27">
-        <v>0.15729599999999999</v>
+        <v>0.251363</v>
       </c>
       <c r="BB27">
-        <v>0.139464</v>
+        <v>0.22289600000000001</v>
       </c>
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.25">
@@ -7531,58 +7531,58 @@
         <v>18.474619000000001</v>
       </c>
       <c r="AK28">
-        <v>7.1098999999999996E-2</v>
+        <v>0.11372500000000001</v>
       </c>
       <c r="AL28">
-        <v>7.2926000000000005E-2</v>
+        <v>0.116677</v>
       </c>
       <c r="AM28">
-        <v>8.3000000000000004E-2</v>
+        <v>0.13330400000000001</v>
       </c>
       <c r="AN28">
-        <v>8.3065E-2</v>
+        <v>0.132299</v>
       </c>
       <c r="AO28">
-        <v>8.4940000000000002E-2</v>
+        <v>0.134128</v>
       </c>
       <c r="AP28">
-        <v>7.1248000000000006E-2</v>
+        <v>0.11394899999999999</v>
       </c>
       <c r="AQ28">
-        <v>7.7699000000000004E-2</v>
+        <v>0.12528400000000001</v>
       </c>
       <c r="AR28">
-        <v>8.2237000000000005E-2</v>
+        <v>0.130578</v>
       </c>
       <c r="AS28">
-        <v>8.9369000000000004E-2</v>
+        <v>0.143487</v>
       </c>
       <c r="AT28">
-        <v>9.4756999999999994E-2</v>
+        <v>0.15085000000000001</v>
       </c>
       <c r="AU28">
-        <v>9.4777E-2</v>
+        <v>0.151064</v>
       </c>
       <c r="AV28">
-        <v>8.4639000000000006E-2</v>
+        <v>0.13519999999999999</v>
       </c>
       <c r="AW28">
-        <v>0.133632</v>
+        <v>0.21409900000000001</v>
       </c>
       <c r="AX28">
-        <v>0.140265</v>
+        <v>0.22475899999999999</v>
       </c>
       <c r="AY28">
-        <v>0.15713199999999999</v>
+        <v>0.25308900000000001</v>
       </c>
       <c r="AZ28">
-        <v>0.16395599999999999</v>
+        <v>0.26215500000000003</v>
       </c>
       <c r="BA28">
-        <v>0.15751499999999999</v>
+        <v>0.252054</v>
       </c>
       <c r="BB28">
-        <v>0.13902900000000001</v>
+        <v>0.22223599999999999</v>
       </c>
     </row>
     <row r="29" spans="1:54" x14ac:dyDescent="0.25">
@@ -7695,58 +7695,58 @@
         <v>19.592939999999999</v>
       </c>
       <c r="AK29">
-        <v>7.0064000000000001E-2</v>
+        <v>0.112099</v>
       </c>
       <c r="AL29">
-        <v>7.2789000000000006E-2</v>
+        <v>0.11647299999999999</v>
       </c>
       <c r="AM29">
-        <v>8.1348000000000004E-2</v>
+        <v>0.12908800000000001</v>
       </c>
       <c r="AN29">
-        <v>8.2054000000000002E-2</v>
+        <v>0.129993</v>
       </c>
       <c r="AO29">
-        <v>8.7767999999999999E-2</v>
+        <v>0.137379</v>
       </c>
       <c r="AP29">
-        <v>7.1951000000000001E-2</v>
+        <v>0.11502900000000001</v>
       </c>
       <c r="AQ29">
-        <v>7.7607999999999996E-2</v>
+        <v>0.123489</v>
       </c>
       <c r="AR29">
-        <v>8.1101000000000006E-2</v>
+        <v>0.13011400000000001</v>
       </c>
       <c r="AS29">
-        <v>8.6635000000000004E-2</v>
+        <v>0.139181</v>
       </c>
       <c r="AT29">
-        <v>9.4142000000000003E-2</v>
+        <v>0.14916699999999999</v>
       </c>
       <c r="AU29">
-        <v>9.6750000000000003E-2</v>
+        <v>0.153387</v>
       </c>
       <c r="AV29">
-        <v>8.5667999999999994E-2</v>
+        <v>0.136569</v>
       </c>
       <c r="AW29">
-        <v>0.135188</v>
+        <v>0.216138</v>
       </c>
       <c r="AX29">
-        <v>0.14110500000000001</v>
+        <v>0.225913</v>
       </c>
       <c r="AY29">
-        <v>0.147949</v>
+        <v>0.24625</v>
       </c>
       <c r="AZ29">
-        <v>0.16178799999999999</v>
+        <v>0.25668600000000003</v>
       </c>
       <c r="BA29">
-        <v>0.157864</v>
+        <v>0.25335000000000002</v>
       </c>
       <c r="BB29">
-        <v>0.139764</v>
+        <v>0.223778</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -7859,58 +7859,58 @@
         <v>22.266037000000001</v>
       </c>
       <c r="AK30">
-        <v>6.9983000000000004E-2</v>
+        <v>0.111968</v>
       </c>
       <c r="AL30">
-        <v>7.4221999999999996E-2</v>
+        <v>0.118746</v>
       </c>
       <c r="AM30">
-        <v>8.2770999999999997E-2</v>
+        <v>0.132938</v>
       </c>
       <c r="AN30">
-        <v>8.4844000000000003E-2</v>
+        <v>0.13628599999999999</v>
       </c>
       <c r="AO30">
-        <v>8.6744000000000002E-2</v>
+        <v>0.136461</v>
       </c>
       <c r="AP30">
-        <v>7.2713E-2</v>
+        <v>0.116214</v>
       </c>
       <c r="AQ30">
-        <v>7.9339999999999994E-2</v>
+        <v>0.12970200000000001</v>
       </c>
       <c r="AR30">
-        <v>8.3400000000000002E-2</v>
+        <v>0.13275899999999999</v>
       </c>
       <c r="AS30">
-        <v>9.6657999999999994E-2</v>
+        <v>0.15409</v>
       </c>
       <c r="AT30">
-        <v>9.7156999999999993E-2</v>
+        <v>0.15618099999999999</v>
       </c>
       <c r="AU30">
-        <v>9.9784999999999999E-2</v>
+        <v>0.15634600000000001</v>
       </c>
       <c r="AV30">
-        <v>8.6475999999999997E-2</v>
+        <v>0.137714</v>
       </c>
       <c r="AW30">
-        <v>0.135986</v>
+        <v>0.217334</v>
       </c>
       <c r="AX30">
-        <v>0.1431</v>
+        <v>0.22942899999999999</v>
       </c>
       <c r="AY30">
-        <v>0.16292799999999999</v>
+        <v>0.25856099999999999</v>
       </c>
       <c r="AZ30">
-        <v>0.169797</v>
+        <v>0.27004099999999998</v>
       </c>
       <c r="BA30">
-        <v>0.16169</v>
+        <v>0.258127</v>
       </c>
       <c r="BB30">
-        <v>0.13906399999999999</v>
+        <v>0.22228999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -8023,58 +8023,58 @@
         <v>23.726150000000001</v>
       </c>
       <c r="AK31">
-        <v>6.9663000000000003E-2</v>
+        <v>0.111467</v>
       </c>
       <c r="AL31">
-        <v>7.4854000000000004E-2</v>
+        <v>0.119751</v>
       </c>
       <c r="AM31">
-        <v>8.3639000000000005E-2</v>
+        <v>0.13519400000000001</v>
       </c>
       <c r="AN31">
-        <v>8.6481000000000002E-2</v>
+        <v>0.139846</v>
       </c>
       <c r="AO31">
-        <v>8.3528000000000005E-2</v>
+        <v>0.133072</v>
       </c>
       <c r="AP31">
-        <v>7.2919999999999999E-2</v>
+        <v>0.1166</v>
       </c>
       <c r="AQ31">
-        <v>8.0171999999999993E-2</v>
+        <v>0.129968</v>
       </c>
       <c r="AR31">
-        <v>8.4885000000000002E-2</v>
+        <v>0.13453999999999999</v>
       </c>
       <c r="AS31">
-        <v>9.9792000000000006E-2</v>
+        <v>0.157885</v>
       </c>
       <c r="AT31">
-        <v>9.8971000000000003E-2</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="AU31">
-        <v>9.9728999999999998E-2</v>
+        <v>0.15679899999999999</v>
       </c>
       <c r="AV31">
-        <v>8.7594000000000005E-2</v>
+        <v>0.13902900000000001</v>
       </c>
       <c r="AW31">
-        <v>0.13761200000000001</v>
+        <v>0.21933900000000001</v>
       </c>
       <c r="AX31">
-        <v>0.14498800000000001</v>
+        <v>0.23293700000000001</v>
       </c>
       <c r="AY31">
-        <v>0.16971700000000001</v>
+        <v>0.26657500000000001</v>
       </c>
       <c r="AZ31">
-        <v>0.176505</v>
+        <v>0.27917500000000001</v>
       </c>
       <c r="BA31">
-        <v>0.162497</v>
+        <v>0.25983600000000001</v>
       </c>
       <c r="BB31">
-        <v>0.13909199999999999</v>
+        <v>0.22223200000000001</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -8541,58 +8541,58 @@
         <v>18.469467999999999</v>
       </c>
       <c r="AK3">
-        <v>7.0571999999999996E-2</v>
+        <v>0.112925</v>
       </c>
       <c r="AL3">
-        <v>6.9114999999999996E-2</v>
+        <v>0.110611</v>
       </c>
       <c r="AM3">
-        <v>7.1849999999999997E-2</v>
+        <v>0.110732</v>
       </c>
       <c r="AN3">
-        <v>7.3626999999999998E-2</v>
+        <v>0.114358</v>
       </c>
       <c r="AO3">
-        <v>7.3176000000000005E-2</v>
+        <v>0.118968</v>
       </c>
       <c r="AP3">
-        <v>7.1936E-2</v>
+        <v>0.115081</v>
       </c>
       <c r="AQ3">
-        <v>8.3825999999999998E-2</v>
+        <v>0.135772</v>
       </c>
       <c r="AR3">
-        <v>7.9604999999999995E-2</v>
+        <v>0.12722</v>
       </c>
       <c r="AS3">
-        <v>7.3786000000000004E-2</v>
+        <v>0.122504</v>
       </c>
       <c r="AT3">
-        <v>8.7069999999999995E-2</v>
+        <v>0.13703799999999999</v>
       </c>
       <c r="AU3">
-        <v>8.6509000000000003E-2</v>
+        <v>0.142817</v>
       </c>
       <c r="AV3">
-        <v>8.3503999999999995E-2</v>
+        <v>0.13339999999999999</v>
       </c>
       <c r="AW3">
-        <v>0.130547</v>
+        <v>0.20985899999999999</v>
       </c>
       <c r="AX3">
-        <v>0.13241800000000001</v>
+        <v>0.21126</v>
       </c>
       <c r="AY3">
-        <v>0.12643699999999999</v>
+        <v>0.210393</v>
       </c>
       <c r="AZ3">
-        <v>0.145565</v>
+        <v>0.239006</v>
       </c>
       <c r="BA3">
-        <v>0.15113799999999999</v>
+        <v>0.24355099999999999</v>
       </c>
       <c r="BB3">
-        <v>0.144871</v>
+        <v>0.23321800000000001</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.25">
@@ -8705,58 +8705,58 @@
         <v>16.10763</v>
       </c>
       <c r="AK4">
-        <v>7.0394999999999999E-2</v>
+        <v>0.11264200000000001</v>
       </c>
       <c r="AL4">
-        <v>6.9334000000000007E-2</v>
+        <v>0.11096</v>
       </c>
       <c r="AM4">
-        <v>7.3338E-2</v>
+        <v>0.11514199999999999</v>
       </c>
       <c r="AN4">
-        <v>7.4090000000000003E-2</v>
+        <v>0.115703</v>
       </c>
       <c r="AO4">
-        <v>7.3871000000000006E-2</v>
+        <v>0.119654</v>
       </c>
       <c r="AP4">
-        <v>7.2228000000000001E-2</v>
+        <v>0.11557099999999999</v>
       </c>
       <c r="AQ4">
-        <v>8.3509E-2</v>
+        <v>0.13389999999999999</v>
       </c>
       <c r="AR4">
-        <v>7.8840999999999994E-2</v>
+        <v>0.12642800000000001</v>
       </c>
       <c r="AS4">
-        <v>7.5504000000000002E-2</v>
+        <v>0.12506300000000001</v>
       </c>
       <c r="AT4">
-        <v>8.6785000000000001E-2</v>
+        <v>0.13675799999999999</v>
       </c>
       <c r="AU4">
-        <v>8.8233000000000006E-2</v>
+        <v>0.14426600000000001</v>
       </c>
       <c r="AV4">
-        <v>8.2951999999999998E-2</v>
+        <v>0.13299</v>
       </c>
       <c r="AW4">
-        <v>0.13127</v>
+        <v>0.210729</v>
       </c>
       <c r="AX4">
-        <v>0.132801</v>
+        <v>0.21201600000000001</v>
       </c>
       <c r="AY4">
-        <v>0.132385</v>
+        <v>0.213729</v>
       </c>
       <c r="AZ4">
-        <v>0.147035</v>
+        <v>0.24241699999999999</v>
       </c>
       <c r="BA4">
-        <v>0.15145</v>
+        <v>0.244034</v>
       </c>
       <c r="BB4">
-        <v>0.142537</v>
+        <v>0.22859499999999999</v>
       </c>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.25">
@@ -8869,58 +8869,58 @@
         <v>13.70266</v>
       </c>
       <c r="AK5">
-        <v>7.0549000000000001E-2</v>
+        <v>0.11287999999999999</v>
       </c>
       <c r="AL5">
-        <v>6.9610000000000005E-2</v>
+        <v>0.1114</v>
       </c>
       <c r="AM5">
-        <v>7.467E-2</v>
+        <v>0.119017</v>
       </c>
       <c r="AN5">
-        <v>7.5360999999999997E-2</v>
+        <v>0.11873599999999999</v>
       </c>
       <c r="AO5">
-        <v>7.5270000000000004E-2</v>
+        <v>0.12119000000000001</v>
       </c>
       <c r="AP5">
-        <v>7.3066000000000006E-2</v>
+        <v>0.116879</v>
       </c>
       <c r="AQ5">
-        <v>8.3426E-2</v>
+        <v>0.13508300000000001</v>
       </c>
       <c r="AR5">
-        <v>7.8345999999999999E-2</v>
+        <v>0.12606899999999999</v>
       </c>
       <c r="AS5">
-        <v>7.8628000000000003E-2</v>
+        <v>0.12898599999999999</v>
       </c>
       <c r="AT5">
-        <v>8.7596999999999994E-2</v>
+        <v>0.13875999999999999</v>
       </c>
       <c r="AU5">
-        <v>9.1128000000000001E-2</v>
+        <v>0.146813</v>
       </c>
       <c r="AV5">
-        <v>8.3259E-2</v>
+        <v>0.133601</v>
       </c>
       <c r="AW5">
-        <v>0.13315299999999999</v>
+        <v>0.21308299999999999</v>
       </c>
       <c r="AX5">
-        <v>0.133658</v>
+        <v>0.21352299999999999</v>
       </c>
       <c r="AY5">
-        <v>0.13977800000000001</v>
+        <v>0.219718</v>
       </c>
       <c r="AZ5">
-        <v>0.151447</v>
+        <v>0.248976</v>
       </c>
       <c r="BA5">
-        <v>0.15437500000000001</v>
+        <v>0.247673</v>
       </c>
       <c r="BB5">
-        <v>0.141766</v>
+        <v>0.22694500000000001</v>
       </c>
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.25">
@@ -9033,58 +9033,58 @@
         <v>14.001236</v>
       </c>
       <c r="AK6">
-        <v>7.084E-2</v>
+        <v>0.11333500000000001</v>
       </c>
       <c r="AL6">
-        <v>6.9751999999999995E-2</v>
+        <v>0.111634</v>
       </c>
       <c r="AM6">
-        <v>7.3444999999999996E-2</v>
+        <v>0.115644</v>
       </c>
       <c r="AN6">
-        <v>7.6199000000000003E-2</v>
+        <v>0.12027400000000001</v>
       </c>
       <c r="AO6">
-        <v>7.5757000000000005E-2</v>
+        <v>0.122021</v>
       </c>
       <c r="AP6">
-        <v>7.4160000000000004E-2</v>
+        <v>0.118571</v>
       </c>
       <c r="AQ6">
-        <v>8.2664000000000001E-2</v>
+        <v>0.13259899999999999</v>
       </c>
       <c r="AR6">
-        <v>7.8079999999999997E-2</v>
+        <v>0.12623799999999999</v>
       </c>
       <c r="AS6">
-        <v>7.6205999999999996E-2</v>
+        <v>0.12463100000000001</v>
       </c>
       <c r="AT6">
-        <v>8.8522000000000003E-2</v>
+        <v>0.14038700000000001</v>
       </c>
       <c r="AU6">
-        <v>9.3536999999999995E-2</v>
+        <v>0.14934</v>
       </c>
       <c r="AV6">
-        <v>8.4859000000000004E-2</v>
+        <v>0.13563800000000001</v>
       </c>
       <c r="AW6">
-        <v>0.134046</v>
+        <v>0.21442</v>
       </c>
       <c r="AX6">
-        <v>0.13422300000000001</v>
+        <v>0.214197</v>
       </c>
       <c r="AY6">
-        <v>0.133241</v>
+        <v>0.21775900000000001</v>
       </c>
       <c r="AZ6">
-        <v>0.15279699999999999</v>
+        <v>0.24778800000000001</v>
       </c>
       <c r="BA6">
-        <v>0.15656</v>
+        <v>0.25137900000000002</v>
       </c>
       <c r="BB6">
-        <v>0.142483</v>
+        <v>0.228126</v>
       </c>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.25">
@@ -9197,58 +9197,58 @@
         <v>15.995520000000001</v>
       </c>
       <c r="AK7">
-        <v>7.0890999999999996E-2</v>
+        <v>0.113417</v>
       </c>
       <c r="AL7">
-        <v>7.1234000000000006E-2</v>
+        <v>0.113991</v>
       </c>
       <c r="AM7">
-        <v>7.3274000000000006E-2</v>
+        <v>0.114648</v>
       </c>
       <c r="AN7">
-        <v>7.8392000000000003E-2</v>
+        <v>0.12461800000000001</v>
       </c>
       <c r="AO7">
-        <v>7.6934000000000002E-2</v>
+        <v>0.123709</v>
       </c>
       <c r="AP7">
-        <v>7.4018E-2</v>
+        <v>0.118515</v>
       </c>
       <c r="AQ7">
-        <v>8.1848000000000004E-2</v>
+        <v>0.12970699999999999</v>
       </c>
       <c r="AR7">
-        <v>8.0321000000000004E-2</v>
+        <v>0.128964</v>
       </c>
       <c r="AS7">
-        <v>7.7940999999999996E-2</v>
+        <v>0.126772</v>
       </c>
       <c r="AT7">
-        <v>9.0962000000000001E-2</v>
+        <v>0.145366</v>
       </c>
       <c r="AU7">
-        <v>9.4172000000000006E-2</v>
+        <v>0.15088599999999999</v>
       </c>
       <c r="AV7">
-        <v>8.5915000000000005E-2</v>
+        <v>0.13724</v>
       </c>
       <c r="AW7">
-        <v>0.13514899999999999</v>
+        <v>0.21606400000000001</v>
       </c>
       <c r="AX7">
-        <v>0.13744899999999999</v>
+        <v>0.220031</v>
       </c>
       <c r="AY7">
-        <v>0.137659</v>
+        <v>0.22514500000000001</v>
       </c>
       <c r="AZ7">
-        <v>0.15962399999999999</v>
+        <v>0.25757400000000003</v>
       </c>
       <c r="BA7">
-        <v>0.16212199999999999</v>
+        <v>0.258739</v>
       </c>
       <c r="BB7">
-        <v>0.14391699999999999</v>
+        <v>0.23064599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.25">
@@ -9361,58 +9361,58 @@
         <v>17.253026999999999</v>
       </c>
       <c r="AK8">
-        <v>7.1114999999999998E-2</v>
+        <v>0.113771</v>
       </c>
       <c r="AL8">
-        <v>7.3635999999999993E-2</v>
+        <v>0.117801</v>
       </c>
       <c r="AM8">
-        <v>7.5745000000000007E-2</v>
+        <v>0.120264</v>
       </c>
       <c r="AN8">
-        <v>8.1595000000000001E-2</v>
+        <v>0.13119800000000001</v>
       </c>
       <c r="AO8">
-        <v>7.9889000000000002E-2</v>
+        <v>0.12720899999999999</v>
       </c>
       <c r="AP8">
-        <v>7.5212000000000001E-2</v>
+        <v>0.12037399999999999</v>
       </c>
       <c r="AQ8">
-        <v>8.2017000000000007E-2</v>
+        <v>0.130748</v>
       </c>
       <c r="AR8">
-        <v>8.4227999999999997E-2</v>
+        <v>0.133358</v>
       </c>
       <c r="AS8">
-        <v>8.6780999999999997E-2</v>
+        <v>0.13941799999999999</v>
       </c>
       <c r="AT8">
-        <v>9.3828999999999996E-2</v>
+        <v>0.15124399999999999</v>
       </c>
       <c r="AU8">
-        <v>9.7550999999999999E-2</v>
+        <v>0.15413199999999999</v>
       </c>
       <c r="AV8">
-        <v>8.9391999999999999E-2</v>
+        <v>0.14118800000000001</v>
       </c>
       <c r="AW8">
-        <v>0.13783699999999999</v>
+        <v>0.21949399999999999</v>
       </c>
       <c r="AX8">
-        <v>0.141537</v>
+        <v>0.22750999999999999</v>
       </c>
       <c r="AY8">
-        <v>0.15215899999999999</v>
+        <v>0.24183199999999999</v>
       </c>
       <c r="AZ8">
-        <v>0.168238</v>
+        <v>0.27038000000000001</v>
       </c>
       <c r="BA8">
-        <v>0.170958</v>
+        <v>0.26911099999999999</v>
       </c>
       <c r="BB8">
-        <v>0.14713000000000001</v>
+        <v>0.23680399999999999</v>
       </c>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.25">
@@ -9525,58 +9525,58 @@
         <v>17.693346999999999</v>
       </c>
       <c r="AK9">
-        <v>7.1429999999999993E-2</v>
+        <v>0.11426699999999999</v>
       </c>
       <c r="AL9">
-        <v>7.5550999999999993E-2</v>
+        <v>0.120836</v>
       </c>
       <c r="AM9">
-        <v>7.8190999999999997E-2</v>
+        <v>0.12585499999999999</v>
       </c>
       <c r="AN9">
-        <v>8.2812999999999998E-2</v>
+        <v>0.13336899999999999</v>
       </c>
       <c r="AO9">
-        <v>8.0728999999999995E-2</v>
+        <v>0.128416</v>
       </c>
       <c r="AP9">
-        <v>7.6004000000000002E-2</v>
+        <v>0.121623</v>
       </c>
       <c r="AQ9">
-        <v>8.2325999999999996E-2</v>
+        <v>0.131434</v>
       </c>
       <c r="AR9">
-        <v>8.7448999999999999E-2</v>
+        <v>0.13680600000000001</v>
       </c>
       <c r="AS9">
-        <v>9.3205999999999997E-2</v>
+        <v>0.14821300000000001</v>
       </c>
       <c r="AT9">
-        <v>9.4952999999999996E-2</v>
+        <v>0.15309600000000001</v>
       </c>
       <c r="AU9">
-        <v>9.8657999999999996E-2</v>
+        <v>0.15546199999999999</v>
       </c>
       <c r="AV9">
-        <v>9.1415999999999997E-2</v>
+        <v>0.14342099999999999</v>
       </c>
       <c r="AW9">
-        <v>0.139684</v>
+        <v>0.221751</v>
       </c>
       <c r="AX9">
-        <v>0.14482700000000001</v>
+        <v>0.23366799999999999</v>
       </c>
       <c r="AY9">
-        <v>0.16495099999999999</v>
+        <v>0.25595499999999999</v>
       </c>
       <c r="AZ9">
-        <v>0.17061499999999999</v>
+        <v>0.27106999999999998</v>
       </c>
       <c r="BA9">
-        <v>0.17256299999999999</v>
+        <v>0.27180399999999999</v>
       </c>
       <c r="BB9">
-        <v>0.148817</v>
+        <v>0.240097</v>
       </c>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.25">
@@ -9689,58 +9689,58 @@
         <v>22.915690000000001</v>
       </c>
       <c r="AK10">
-        <v>7.2077000000000002E-2</v>
+        <v>0.11529300000000001</v>
       </c>
       <c r="AL10">
-        <v>6.9690000000000002E-2</v>
+        <v>0.11151800000000001</v>
       </c>
       <c r="AM10">
-        <v>7.7184000000000003E-2</v>
+        <v>0.122501</v>
       </c>
       <c r="AN10">
-        <v>8.0418000000000003E-2</v>
+        <v>0.12834999999999999</v>
       </c>
       <c r="AO10">
-        <v>7.7199000000000004E-2</v>
+        <v>0.123469</v>
       </c>
       <c r="AP10">
-        <v>7.0668999999999996E-2</v>
+        <v>0.11301700000000001</v>
       </c>
       <c r="AQ10">
-        <v>7.9487000000000002E-2</v>
+        <v>0.125191</v>
       </c>
       <c r="AR10">
-        <v>7.9891000000000004E-2</v>
+        <v>0.12731500000000001</v>
       </c>
       <c r="AS10">
-        <v>8.3978999999999998E-2</v>
+        <v>0.136072</v>
       </c>
       <c r="AT10">
-        <v>9.3148999999999996E-2</v>
+        <v>0.14973800000000001</v>
       </c>
       <c r="AU10">
-        <v>9.0758000000000005E-2</v>
+        <v>0.145536</v>
       </c>
       <c r="AV10">
-        <v>8.165E-2</v>
+        <v>0.131027</v>
       </c>
       <c r="AW10">
-        <v>0.131546</v>
+        <v>0.21091799999999999</v>
       </c>
       <c r="AX10">
-        <v>0.132742</v>
+        <v>0.21213499999999999</v>
       </c>
       <c r="AY10">
-        <v>0.14882400000000001</v>
+        <v>0.23368700000000001</v>
       </c>
       <c r="AZ10">
-        <v>0.15826699999999999</v>
+        <v>0.25653900000000002</v>
       </c>
       <c r="BA10">
-        <v>0.156087</v>
+        <v>0.248109</v>
       </c>
       <c r="BB10">
-        <v>0.14265700000000001</v>
+        <v>0.22911699999999999</v>
       </c>
     </row>
     <row r="11" spans="1:54" x14ac:dyDescent="0.25">
@@ -9853,58 +9853,58 @@
         <v>20.284220999999999</v>
       </c>
       <c r="AK11">
-        <v>7.0841000000000001E-2</v>
+        <v>0.113347</v>
       </c>
       <c r="AL11">
-        <v>6.9091E-2</v>
+        <v>0.11057</v>
       </c>
       <c r="AM11">
-        <v>7.5743000000000005E-2</v>
+        <v>0.119309</v>
       </c>
       <c r="AN11">
-        <v>7.7146000000000006E-2</v>
+        <v>0.12128800000000001</v>
       </c>
       <c r="AO11">
-        <v>7.5534000000000004E-2</v>
+        <v>0.121554</v>
       </c>
       <c r="AP11">
-        <v>6.9665000000000005E-2</v>
+        <v>0.111549</v>
       </c>
       <c r="AQ11">
-        <v>7.9139000000000001E-2</v>
+        <v>0.126133</v>
       </c>
       <c r="AR11">
-        <v>7.7618999999999994E-2</v>
+        <v>0.124904</v>
       </c>
       <c r="AS11">
-        <v>7.5421000000000002E-2</v>
+        <v>0.123016</v>
       </c>
       <c r="AT11">
-        <v>8.8940000000000005E-2</v>
+        <v>0.14036499999999999</v>
       </c>
       <c r="AU11">
-        <v>8.931E-2</v>
+        <v>0.144285</v>
       </c>
       <c r="AV11">
-        <v>7.9800999999999997E-2</v>
+        <v>0.129</v>
       </c>
       <c r="AW11">
-        <v>0.12865099999999999</v>
+        <v>0.20733099999999999</v>
       </c>
       <c r="AX11">
-        <v>0.129853</v>
+        <v>0.20664399999999999</v>
       </c>
       <c r="AY11">
-        <v>0.13003100000000001</v>
+        <v>0.217088</v>
       </c>
       <c r="AZ11">
-        <v>0.14658599999999999</v>
+        <v>0.23588100000000001</v>
       </c>
       <c r="BA11">
-        <v>0.14988299999999999</v>
+        <v>0.24130599999999999</v>
       </c>
       <c r="BB11">
-        <v>0.137572</v>
+        <v>0.21929899999999999</v>
       </c>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.25">
@@ -10017,58 +10017,58 @@
         <v>16.071721</v>
       </c>
       <c r="AK12">
-        <v>6.9744E-2</v>
+        <v>0.11161600000000001</v>
       </c>
       <c r="AL12">
-        <v>6.9262000000000004E-2</v>
+        <v>0.110844</v>
       </c>
       <c r="AM12">
-        <v>7.5740000000000002E-2</v>
+        <v>0.119807</v>
       </c>
       <c r="AN12">
-        <v>7.5957999999999998E-2</v>
+        <v>0.11896</v>
       </c>
       <c r="AO12">
-        <v>7.3122000000000006E-2</v>
+        <v>0.11906</v>
       </c>
       <c r="AP12">
-        <v>6.9295999999999996E-2</v>
+        <v>0.11101900000000001</v>
       </c>
       <c r="AQ12">
-        <v>7.7826999999999993E-2</v>
+        <v>0.120106</v>
       </c>
       <c r="AR12">
-        <v>7.5916999999999998E-2</v>
+        <v>0.1231</v>
       </c>
       <c r="AS12">
-        <v>7.0292999999999994E-2</v>
+        <v>0.115312</v>
       </c>
       <c r="AT12">
-        <v>8.6414000000000005E-2</v>
+        <v>0.134938</v>
       </c>
       <c r="AU12">
-        <v>8.6960999999999997E-2</v>
+        <v>0.14282800000000001</v>
       </c>
       <c r="AV12">
-        <v>7.8703999999999996E-2</v>
+        <v>0.12795899999999999</v>
       </c>
       <c r="AW12">
-        <v>0.12693099999999999</v>
+        <v>0.20522799999999999</v>
       </c>
       <c r="AX12">
-        <v>0.129603</v>
+        <v>0.20627999999999999</v>
       </c>
       <c r="AY12">
-        <v>0.124956</v>
+        <v>0.210952</v>
       </c>
       <c r="AZ12">
-        <v>0.14136299999999999</v>
+        <v>0.22738800000000001</v>
       </c>
       <c r="BA12">
-        <v>0.14233000000000001</v>
+        <v>0.23366300000000001</v>
       </c>
       <c r="BB12">
-        <v>0.133076</v>
+        <v>0.21059800000000001</v>
       </c>
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.25">
@@ -10181,58 +10181,58 @@
         <v>15.72231</v>
       </c>
       <c r="AK13">
-        <v>6.9527000000000005E-2</v>
+        <v>0.111266</v>
       </c>
       <c r="AL13">
-        <v>7.0569000000000007E-2</v>
+        <v>0.112917</v>
       </c>
       <c r="AM13">
-        <v>7.6730000000000007E-2</v>
+        <v>0.123015</v>
       </c>
       <c r="AN13">
-        <v>7.8259999999999996E-2</v>
+        <v>0.12464699999999999</v>
       </c>
       <c r="AO13">
-        <v>7.5441999999999995E-2</v>
+        <v>0.121544</v>
       </c>
       <c r="AP13">
-        <v>7.0247000000000004E-2</v>
+        <v>0.112443</v>
       </c>
       <c r="AQ13">
-        <v>7.8431000000000001E-2</v>
+        <v>0.12521499999999999</v>
       </c>
       <c r="AR13">
-        <v>7.7030000000000001E-2</v>
+        <v>0.12404900000000001</v>
       </c>
       <c r="AS13">
-        <v>7.3905999999999999E-2</v>
+        <v>0.12083199999999999</v>
       </c>
       <c r="AT13">
-        <v>8.8025000000000006E-2</v>
+        <v>0.13934099999999999</v>
       </c>
       <c r="AU13">
-        <v>8.9580000000000007E-2</v>
+        <v>0.14519599999999999</v>
       </c>
       <c r="AV13">
-        <v>8.3060999999999996E-2</v>
+        <v>0.132575</v>
       </c>
       <c r="AW13">
-        <v>0.127771</v>
+        <v>0.206312</v>
       </c>
       <c r="AX13">
-        <v>0.130163</v>
+        <v>0.20727400000000001</v>
       </c>
       <c r="AY13">
-        <v>0.13716500000000001</v>
+        <v>0.218112</v>
       </c>
       <c r="AZ13">
-        <v>0.14777199999999999</v>
+        <v>0.24104900000000001</v>
       </c>
       <c r="BA13">
-        <v>0.14651700000000001</v>
+        <v>0.23805699999999999</v>
       </c>
       <c r="BB13">
-        <v>0.134604</v>
+        <v>0.213757</v>
       </c>
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.25">
@@ -10345,58 +10345,58 @@
         <v>16.943283000000001</v>
       </c>
       <c r="AK14">
-        <v>6.9178000000000003E-2</v>
+        <v>0.110712</v>
       </c>
       <c r="AL14">
-        <v>7.0572999999999997E-2</v>
+        <v>0.11293599999999999</v>
       </c>
       <c r="AM14">
-        <v>7.4917999999999998E-2</v>
+        <v>0.11835900000000001</v>
       </c>
       <c r="AN14">
-        <v>7.7973000000000001E-2</v>
+        <v>0.123741</v>
       </c>
       <c r="AO14">
-        <v>7.5986999999999999E-2</v>
+        <v>0.12254900000000001</v>
       </c>
       <c r="AP14">
-        <v>7.1114999999999998E-2</v>
+        <v>0.11380800000000001</v>
       </c>
       <c r="AQ14">
-        <v>7.8397999999999995E-2</v>
+        <v>0.12449200000000001</v>
       </c>
       <c r="AR14">
-        <v>7.5537999999999994E-2</v>
+        <v>0.12310400000000001</v>
       </c>
       <c r="AS14">
-        <v>7.4463000000000001E-2</v>
+        <v>0.12156400000000001</v>
       </c>
       <c r="AT14">
-        <v>8.8927999999999993E-2</v>
+        <v>0.14108799999999999</v>
       </c>
       <c r="AU14">
-        <v>9.1560000000000002E-2</v>
+        <v>0.14771400000000001</v>
       </c>
       <c r="AV14">
-        <v>8.3059999999999995E-2</v>
+        <v>0.13308700000000001</v>
       </c>
       <c r="AW14">
-        <v>0.129605</v>
+        <v>0.20880099999999999</v>
       </c>
       <c r="AX14">
-        <v>0.12951799999999999</v>
+        <v>0.20552200000000001</v>
       </c>
       <c r="AY14">
-        <v>0.13083600000000001</v>
+        <v>0.21466399999999999</v>
       </c>
       <c r="AZ14">
-        <v>0.15015100000000001</v>
+        <v>0.24385999999999999</v>
       </c>
       <c r="BA14">
-        <v>0.14951300000000001</v>
+        <v>0.24260699999999999</v>
       </c>
       <c r="BB14">
-        <v>0.137156</v>
+        <v>0.21856900000000001</v>
       </c>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
@@ -10509,58 +10509,58 @@
         <v>17.554789</v>
       </c>
       <c r="AK15">
-        <v>6.9142999999999996E-2</v>
+        <v>0.11065700000000001</v>
       </c>
       <c r="AL15">
-        <v>7.0569999999999994E-2</v>
+        <v>0.11294700000000001</v>
       </c>
       <c r="AM15">
-        <v>7.3907E-2</v>
+        <v>0.115246</v>
       </c>
       <c r="AN15">
-        <v>7.8020000000000006E-2</v>
+        <v>0.123184</v>
       </c>
       <c r="AO15">
-        <v>7.6705999999999996E-2</v>
+        <v>0.123886</v>
       </c>
       <c r="AP15">
-        <v>7.1652999999999994E-2</v>
+        <v>0.114732</v>
       </c>
       <c r="AQ15">
-        <v>7.8438999999999995E-2</v>
+        <v>0.123668</v>
       </c>
       <c r="AR15">
-        <v>7.5902999999999998E-2</v>
+        <v>0.124246</v>
       </c>
       <c r="AS15">
-        <v>7.5485999999999998E-2</v>
+        <v>0.122812</v>
       </c>
       <c r="AT15">
-        <v>8.9817999999999995E-2</v>
+        <v>0.14221300000000001</v>
       </c>
       <c r="AU15">
-        <v>9.2318999999999998E-2</v>
+        <v>0.14974699999999999</v>
       </c>
       <c r="AV15">
-        <v>8.3376000000000006E-2</v>
+        <v>0.13391</v>
       </c>
       <c r="AW15">
-        <v>0.13173899999999999</v>
+        <v>0.211788</v>
       </c>
       <c r="AX15">
-        <v>0.13086300000000001</v>
+        <v>0.207459</v>
       </c>
       <c r="AY15">
-        <v>0.12815299999999999</v>
+        <v>0.21651899999999999</v>
       </c>
       <c r="AZ15">
-        <v>0.151362</v>
+        <v>0.242282</v>
       </c>
       <c r="BA15">
-        <v>0.15503400000000001</v>
+        <v>0.25025900000000001</v>
       </c>
       <c r="BB15">
-        <v>0.13972699999999999</v>
+        <v>0.22328600000000001</v>
       </c>
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.25">
@@ -10673,58 +10673,58 @@
         <v>18.603148999999998</v>
       </c>
       <c r="AK16">
-        <v>6.9638000000000005E-2</v>
+        <v>0.11143599999999999</v>
       </c>
       <c r="AL16">
-        <v>7.2767999999999999E-2</v>
+        <v>0.116437</v>
       </c>
       <c r="AM16">
-        <v>7.6744000000000007E-2</v>
+        <v>0.121808</v>
       </c>
       <c r="AN16">
-        <v>8.1073000000000006E-2</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="AO16">
-        <v>8.0082E-2</v>
+        <v>0.12790899999999999</v>
       </c>
       <c r="AP16">
-        <v>7.2223999999999997E-2</v>
+        <v>0.11572300000000001</v>
       </c>
       <c r="AQ16">
-        <v>7.9278000000000001E-2</v>
+        <v>0.124956</v>
       </c>
       <c r="AR16">
-        <v>7.9926999999999998E-2</v>
+        <v>0.12898299999999999</v>
       </c>
       <c r="AS16">
-        <v>8.5168999999999995E-2</v>
+        <v>0.13686999999999999</v>
       </c>
       <c r="AT16">
-        <v>9.2674999999999993E-2</v>
+        <v>0.14799399999999999</v>
       </c>
       <c r="AU16">
-        <v>9.7481999999999999E-2</v>
+        <v>0.15465899999999999</v>
       </c>
       <c r="AV16">
-        <v>8.4010000000000001E-2</v>
+        <v>0.13503399999999999</v>
       </c>
       <c r="AW16">
-        <v>0.13581199999999999</v>
+        <v>0.217004</v>
       </c>
       <c r="AX16">
-        <v>0.136625</v>
+        <v>0.218084</v>
       </c>
       <c r="AY16">
-        <v>0.14593800000000001</v>
+        <v>0.23597399999999999</v>
       </c>
       <c r="AZ16">
-        <v>0.16175700000000001</v>
+        <v>0.25816699999999998</v>
       </c>
       <c r="BA16">
-        <v>0.16478300000000001</v>
+        <v>0.26191900000000001</v>
       </c>
       <c r="BB16">
-        <v>0.14055000000000001</v>
+        <v>0.224519</v>
       </c>
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.25">
@@ -10837,58 +10837,58 @@
         <v>18.310576999999999</v>
       </c>
       <c r="AK17">
-        <v>7.0359000000000005E-2</v>
+        <v>0.112571</v>
       </c>
       <c r="AL17">
-        <v>7.5925999999999993E-2</v>
+        <v>0.121438</v>
       </c>
       <c r="AM17">
-        <v>7.9862000000000002E-2</v>
+        <v>0.12915199999999999</v>
       </c>
       <c r="AN17">
-        <v>8.4043999999999994E-2</v>
+        <v>0.13564599999999999</v>
       </c>
       <c r="AO17">
-        <v>8.2011000000000001E-2</v>
+        <v>0.130246</v>
       </c>
       <c r="AP17">
-        <v>7.3233999999999994E-2</v>
+        <v>0.11731900000000001</v>
       </c>
       <c r="AQ17">
-        <v>8.0730999999999997E-2</v>
+        <v>0.12983500000000001</v>
       </c>
       <c r="AR17">
-        <v>8.6026000000000005E-2</v>
+        <v>0.13526199999999999</v>
       </c>
       <c r="AS17">
-        <v>9.5522999999999997E-2</v>
+        <v>0.151702</v>
       </c>
       <c r="AT17">
-        <v>9.5450999999999994E-2</v>
+        <v>0.153889</v>
       </c>
       <c r="AU17">
-        <v>0.10210900000000001</v>
+        <v>0.158585</v>
       </c>
       <c r="AV17">
-        <v>8.5826E-2</v>
+        <v>0.13716600000000001</v>
       </c>
       <c r="AW17">
-        <v>0.13939199999999999</v>
+        <v>0.22140000000000001</v>
       </c>
       <c r="AX17">
-        <v>0.14318600000000001</v>
+        <v>0.23057800000000001</v>
       </c>
       <c r="AY17">
-        <v>0.16719100000000001</v>
+        <v>0.25712400000000002</v>
       </c>
       <c r="AZ17">
-        <v>0.17228399999999999</v>
+        <v>0.27474100000000001</v>
       </c>
       <c r="BA17">
-        <v>0.169796</v>
+        <v>0.26819599999999999</v>
       </c>
       <c r="BB17">
-        <v>0.14175699999999999</v>
+        <v>0.22672300000000001</v>
       </c>
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.25">
@@ -11001,58 +11001,58 @@
         <v>20.050170000000001</v>
       </c>
       <c r="AK18">
-        <v>7.2109999999999994E-2</v>
+        <v>0.11534700000000001</v>
       </c>
       <c r="AL18">
-        <v>7.1030999999999997E-2</v>
+        <v>0.11364200000000001</v>
       </c>
       <c r="AM18">
-        <v>8.2611000000000004E-2</v>
+        <v>0.13414499999999999</v>
       </c>
       <c r="AN18">
-        <v>8.6967000000000003E-2</v>
+        <v>0.14156099999999999</v>
       </c>
       <c r="AO18">
-        <v>7.9561000000000007E-2</v>
+        <v>0.12642500000000001</v>
       </c>
       <c r="AP18">
-        <v>7.1264999999999995E-2</v>
+        <v>0.113826</v>
       </c>
       <c r="AQ18">
-        <v>7.9888000000000001E-2</v>
+        <v>0.12892500000000001</v>
       </c>
       <c r="AR18">
-        <v>8.0050999999999997E-2</v>
+        <v>0.12750700000000001</v>
       </c>
       <c r="AS18">
-        <v>9.9606E-2</v>
+        <v>0.15759799999999999</v>
       </c>
       <c r="AT18">
-        <v>9.7853999999999997E-2</v>
+        <v>0.15891</v>
       </c>
       <c r="AU18">
-        <v>9.2017000000000002E-2</v>
+        <v>0.14680599999999999</v>
       </c>
       <c r="AV18">
-        <v>8.2661999999999999E-2</v>
+        <v>0.13209199999999999</v>
       </c>
       <c r="AW18">
-        <v>0.13492699999999999</v>
+        <v>0.21509400000000001</v>
       </c>
       <c r="AX18">
-        <v>0.13331699999999999</v>
+        <v>0.21301700000000001</v>
       </c>
       <c r="AY18">
-        <v>0.162329</v>
+        <v>0.25370599999999999</v>
       </c>
       <c r="AZ18">
-        <v>0.17270099999999999</v>
+        <v>0.276418</v>
       </c>
       <c r="BA18">
-        <v>0.15728200000000001</v>
+        <v>0.24985399999999999</v>
       </c>
       <c r="BB18">
-        <v>0.141959</v>
+        <v>0.227744</v>
       </c>
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.25">
@@ -11165,58 +11165,58 @@
         <v>19.373622999999998</v>
       </c>
       <c r="AK19">
-        <v>7.1304000000000006E-2</v>
+        <v>0.114075</v>
       </c>
       <c r="AL19">
-        <v>7.0260000000000003E-2</v>
+        <v>0.112423</v>
       </c>
       <c r="AM19">
-        <v>8.1436999999999996E-2</v>
+        <v>0.131468</v>
       </c>
       <c r="AN19">
-        <v>8.5771E-2</v>
+        <v>0.13919999999999999</v>
       </c>
       <c r="AO19">
-        <v>7.8143000000000004E-2</v>
+        <v>0.124891</v>
       </c>
       <c r="AP19">
-        <v>6.9755999999999999E-2</v>
+        <v>0.11161500000000001</v>
       </c>
       <c r="AQ19">
-        <v>7.9122999999999999E-2</v>
+        <v>0.12767000000000001</v>
       </c>
       <c r="AR19">
-        <v>7.7939999999999995E-2</v>
+        <v>0.125251</v>
       </c>
       <c r="AS19">
-        <v>9.5869999999999997E-2</v>
+        <v>0.152508</v>
       </c>
       <c r="AT19">
-        <v>9.5046000000000005E-2</v>
+        <v>0.153034</v>
       </c>
       <c r="AU19">
-        <v>9.0441999999999995E-2</v>
+        <v>0.145481</v>
       </c>
       <c r="AV19">
-        <v>8.0273999999999998E-2</v>
+        <v>0.129494</v>
       </c>
       <c r="AW19">
-        <v>0.13240299999999999</v>
+        <v>0.21198400000000001</v>
       </c>
       <c r="AX19">
-        <v>0.131076</v>
+        <v>0.20880799999999999</v>
       </c>
       <c r="AY19">
-        <v>0.15574399999999999</v>
+        <v>0.245619</v>
       </c>
       <c r="AZ19">
-        <v>0.167819</v>
+        <v>0.27065499999999998</v>
       </c>
       <c r="BA19">
-        <v>0.153144</v>
+        <v>0.245089</v>
       </c>
       <c r="BB19">
-        <v>0.137325</v>
+        <v>0.21887000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:54" x14ac:dyDescent="0.25">
@@ -11329,58 +11329,58 @@
         <v>16.846245</v>
       </c>
       <c r="AK20">
-        <v>7.0444999999999994E-2</v>
+        <v>0.112717</v>
       </c>
       <c r="AL20">
-        <v>6.9819000000000006E-2</v>
+        <v>0.111731</v>
       </c>
       <c r="AM20">
-        <v>7.9063999999999995E-2</v>
+        <v>0.12576699999999999</v>
       </c>
       <c r="AN20">
-        <v>8.2089999999999996E-2</v>
+        <v>0.131212</v>
       </c>
       <c r="AO20">
-        <v>7.5590000000000004E-2</v>
+        <v>0.122322</v>
       </c>
       <c r="AP20">
-        <v>6.8562999999999999E-2</v>
+        <v>0.109878</v>
       </c>
       <c r="AQ20">
-        <v>7.7838000000000004E-2</v>
+        <v>0.12285799999999999</v>
       </c>
       <c r="AR20">
-        <v>7.5711000000000001E-2</v>
+        <v>0.123031</v>
       </c>
       <c r="AS20">
-        <v>8.3736000000000005E-2</v>
+        <v>0.13439899999999999</v>
       </c>
       <c r="AT20">
-        <v>9.0708999999999998E-2</v>
+        <v>0.14333299999999999</v>
       </c>
       <c r="AU20">
-        <v>8.7109000000000006E-2</v>
+        <v>0.14332400000000001</v>
       </c>
       <c r="AV20">
-        <v>7.8640000000000002E-2</v>
+        <v>0.127834</v>
       </c>
       <c r="AW20">
-        <v>0.13066800000000001</v>
+        <v>0.20983099999999999</v>
       </c>
       <c r="AX20">
-        <v>0.12964999999999999</v>
+        <v>0.206039</v>
       </c>
       <c r="AY20">
-        <v>0.14114499999999999</v>
+        <v>0.232155</v>
       </c>
       <c r="AZ20">
-        <v>0.15531300000000001</v>
+        <v>0.24834999999999999</v>
       </c>
       <c r="BA20">
-        <v>0.14707000000000001</v>
+        <v>0.238788</v>
       </c>
       <c r="BB20">
-        <v>0.133772</v>
+        <v>0.21213299999999999</v>
       </c>
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.25">
@@ -11493,58 +11493,58 @@
         <v>15.897563</v>
       </c>
       <c r="AK21">
-        <v>7.0072999999999996E-2</v>
+        <v>0.112122</v>
       </c>
       <c r="AL21">
-        <v>7.1779999999999997E-2</v>
+        <v>0.11483699999999999</v>
       </c>
       <c r="AM21">
-        <v>7.9987000000000003E-2</v>
+        <v>0.129137</v>
       </c>
       <c r="AN21">
-        <v>8.1762000000000001E-2</v>
+        <v>0.13109499999999999</v>
       </c>
       <c r="AO21">
-        <v>7.6893000000000003E-2</v>
+        <v>0.123834</v>
       </c>
       <c r="AP21">
-        <v>6.8616999999999997E-2</v>
+        <v>0.109983</v>
       </c>
       <c r="AQ21">
-        <v>7.8048999999999993E-2</v>
+        <v>0.126191</v>
       </c>
       <c r="AR21">
-        <v>7.7745999999999996E-2</v>
+        <v>0.124836</v>
       </c>
       <c r="AS21">
-        <v>8.727E-2</v>
+        <v>0.14055400000000001</v>
       </c>
       <c r="AT21">
-        <v>9.1025999999999996E-2</v>
+        <v>0.14490800000000001</v>
       </c>
       <c r="AU21">
-        <v>8.9025999999999994E-2</v>
+        <v>0.14510899999999999</v>
       </c>
       <c r="AV21">
-        <v>7.9979999999999996E-2</v>
+        <v>0.12937899999999999</v>
       </c>
       <c r="AW21">
-        <v>0.13080900000000001</v>
+        <v>0.21002599999999999</v>
       </c>
       <c r="AX21">
-        <v>0.131574</v>
+        <v>0.20977899999999999</v>
       </c>
       <c r="AY21">
-        <v>0.153091</v>
+        <v>0.23690900000000001</v>
       </c>
       <c r="AZ21">
-        <v>0.15638099999999999</v>
+        <v>0.25378699999999998</v>
       </c>
       <c r="BA21">
-        <v>0.14956</v>
+        <v>0.24129800000000001</v>
       </c>
       <c r="BB21">
-        <v>0.13379099999999999</v>
+        <v>0.21230399999999999</v>
       </c>
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.25">
@@ -11657,58 +11657,58 @@
         <v>16.471273</v>
       </c>
       <c r="AK22">
-        <v>6.9603999999999999E-2</v>
+        <v>0.11137900000000001</v>
       </c>
       <c r="AL22">
-        <v>7.2241E-2</v>
+        <v>0.11558</v>
       </c>
       <c r="AM22">
-        <v>7.7309000000000003E-2</v>
+        <v>0.122252</v>
       </c>
       <c r="AN22">
-        <v>7.9620999999999997E-2</v>
+        <v>0.12617100000000001</v>
       </c>
       <c r="AO22">
-        <v>7.7158000000000004E-2</v>
+        <v>0.124639</v>
       </c>
       <c r="AP22">
-        <v>6.9585999999999995E-2</v>
+        <v>0.111456</v>
       </c>
       <c r="AQ22">
-        <v>7.7940999999999996E-2</v>
+        <v>0.12540799999999999</v>
       </c>
       <c r="AR22">
-        <v>7.6680999999999999E-2</v>
+        <v>0.12431300000000001</v>
       </c>
       <c r="AS22">
-        <v>8.0748E-2</v>
+        <v>0.13076599999999999</v>
       </c>
       <c r="AT22">
-        <v>9.0949000000000002E-2</v>
+        <v>0.14453299999999999</v>
       </c>
       <c r="AU22">
-        <v>9.0004000000000001E-2</v>
+        <v>0.14696400000000001</v>
       </c>
       <c r="AV22">
-        <v>8.1542000000000003E-2</v>
+        <v>0.131356</v>
       </c>
       <c r="AW22">
-        <v>0.131271</v>
+        <v>0.21085100000000001</v>
       </c>
       <c r="AX22">
-        <v>0.130912</v>
+        <v>0.20796100000000001</v>
       </c>
       <c r="AY22">
-        <v>0.139407</v>
+        <v>0.226767</v>
       </c>
       <c r="AZ22">
-        <v>0.15313099999999999</v>
+        <v>0.24678600000000001</v>
       </c>
       <c r="BA22">
-        <v>0.149844</v>
+        <v>0.242926</v>
       </c>
       <c r="BB22">
-        <v>0.137041</v>
+        <v>0.21864600000000001</v>
       </c>
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.25">
@@ -11821,58 +11821,58 @@
         <v>16.686387</v>
       </c>
       <c r="AK23">
-        <v>6.9308999999999996E-2</v>
+        <v>0.110912</v>
       </c>
       <c r="AL23">
-        <v>7.1988999999999997E-2</v>
+        <v>0.115199</v>
       </c>
       <c r="AM23">
-        <v>7.6781000000000002E-2</v>
+        <v>0.120683</v>
       </c>
       <c r="AN23">
-        <v>7.9866000000000006E-2</v>
+        <v>0.12637200000000001</v>
       </c>
       <c r="AO23">
-        <v>7.9704999999999998E-2</v>
+        <v>0.12781000000000001</v>
       </c>
       <c r="AP23">
-        <v>7.0322999999999997E-2</v>
+        <v>0.112661</v>
       </c>
       <c r="AQ23">
-        <v>7.8048000000000006E-2</v>
+        <v>0.124125</v>
       </c>
       <c r="AR23">
-        <v>7.6927999999999996E-2</v>
+        <v>0.12537699999999999</v>
       </c>
       <c r="AS23">
-        <v>7.8805E-2</v>
+        <v>0.127746</v>
       </c>
       <c r="AT23">
-        <v>9.1990000000000002E-2</v>
+        <v>0.146341</v>
       </c>
       <c r="AU23">
-        <v>9.3395000000000006E-2</v>
+        <v>0.15082499999999999</v>
       </c>
       <c r="AV23">
-        <v>8.2572000000000007E-2</v>
+        <v>0.132879</v>
       </c>
       <c r="AW23">
-        <v>0.133379</v>
+        <v>0.21374799999999999</v>
       </c>
       <c r="AX23">
-        <v>0.132573</v>
+        <v>0.21052899999999999</v>
       </c>
       <c r="AY23">
-        <v>0.13658400000000001</v>
+        <v>0.22636600000000001</v>
       </c>
       <c r="AZ23">
-        <v>0.155863</v>
+        <v>0.249835</v>
       </c>
       <c r="BA23">
-        <v>0.156445</v>
+        <v>0.251253</v>
       </c>
       <c r="BB23">
-        <v>0.14139399999999999</v>
+        <v>0.22708200000000001</v>
       </c>
     </row>
     <row r="24" spans="1:54" x14ac:dyDescent="0.25">
@@ -11985,58 +11985,58 @@
         <v>22.082291000000001</v>
       </c>
       <c r="AK24">
-        <v>6.9643999999999998E-2</v>
+        <v>0.11144</v>
       </c>
       <c r="AL24">
-        <v>7.5121999999999994E-2</v>
+        <v>0.12016400000000001</v>
       </c>
       <c r="AM24">
-        <v>7.9895999999999995E-2</v>
+        <v>0.12839400000000001</v>
       </c>
       <c r="AN24">
-        <v>8.3964999999999998E-2</v>
+        <v>0.13531799999999999</v>
       </c>
       <c r="AO24">
-        <v>8.2418000000000005E-2</v>
+        <v>0.131027</v>
       </c>
       <c r="AP24">
-        <v>7.1415000000000006E-2</v>
+        <v>0.114401</v>
       </c>
       <c r="AQ24">
-        <v>7.9232999999999998E-2</v>
+        <v>0.12709000000000001</v>
       </c>
       <c r="AR24">
-        <v>8.2589999999999997E-2</v>
+        <v>0.13147600000000001</v>
       </c>
       <c r="AS24">
-        <v>8.6026000000000005E-2</v>
+        <v>0.13810900000000001</v>
       </c>
       <c r="AT24">
-        <v>9.4951999999999995E-2</v>
+        <v>0.15268599999999999</v>
       </c>
       <c r="AU24">
-        <v>9.9843000000000001E-2</v>
+        <v>0.15661900000000001</v>
       </c>
       <c r="AV24">
-        <v>8.3169999999999994E-2</v>
+        <v>0.133964</v>
       </c>
       <c r="AW24">
-        <v>0.13624700000000001</v>
+        <v>0.21751699999999999</v>
       </c>
       <c r="AX24">
-        <v>0.13856099999999999</v>
+        <v>0.221696</v>
       </c>
       <c r="AY24">
-        <v>0.147312</v>
+        <v>0.23911299999999999</v>
       </c>
       <c r="AZ24">
-        <v>0.16592599999999999</v>
+        <v>0.26549499999999998</v>
       </c>
       <c r="BA24">
-        <v>0.16520599999999999</v>
+        <v>0.26166200000000001</v>
       </c>
       <c r="BB24">
-        <v>0.140491</v>
+        <v>0.22486700000000001</v>
       </c>
     </row>
     <row r="25" spans="1:54" x14ac:dyDescent="0.25">
@@ -12149,58 +12149,58 @@
         <v>20.937252999999998</v>
       </c>
       <c r="AK25">
-        <v>7.0180999999999993E-2</v>
+        <v>0.11228399999999999</v>
       </c>
       <c r="AL25">
-        <v>7.7445E-2</v>
+        <v>0.12384299999999999</v>
       </c>
       <c r="AM25">
-        <v>8.1840999999999997E-2</v>
+        <v>0.13289699999999999</v>
       </c>
       <c r="AN25">
-        <v>8.6276000000000005E-2</v>
+        <v>0.14017499999999999</v>
       </c>
       <c r="AO25">
-        <v>8.3187999999999998E-2</v>
+        <v>0.13203799999999999</v>
       </c>
       <c r="AP25">
-        <v>7.3150000000000007E-2</v>
+        <v>0.11703</v>
       </c>
       <c r="AQ25">
-        <v>8.0238000000000004E-2</v>
+        <v>0.128719</v>
       </c>
       <c r="AR25">
-        <v>8.7129999999999999E-2</v>
+        <v>0.13630800000000001</v>
       </c>
       <c r="AS25">
-        <v>9.4298999999999994E-2</v>
+        <v>0.14976999999999999</v>
       </c>
       <c r="AT25">
-        <v>9.6300999999999998E-2</v>
+        <v>0.15514800000000001</v>
       </c>
       <c r="AU25">
-        <v>0.10528999999999999</v>
+        <v>0.16103200000000001</v>
       </c>
       <c r="AV25">
-        <v>8.5384000000000002E-2</v>
+        <v>0.13649700000000001</v>
       </c>
       <c r="AW25">
-        <v>0.139039</v>
+        <v>0.22097700000000001</v>
       </c>
       <c r="AX25">
-        <v>0.14318700000000001</v>
+        <v>0.23036100000000001</v>
       </c>
       <c r="AY25">
-        <v>0.16095999999999999</v>
+        <v>0.253998</v>
       </c>
       <c r="AZ25">
-        <v>0.17377699999999999</v>
+        <v>0.276447</v>
       </c>
       <c r="BA25">
-        <v>0.16625200000000001</v>
+        <v>0.26409100000000002</v>
       </c>
       <c r="BB25">
-        <v>0.14069100000000001</v>
+        <v>0.225047</v>
       </c>
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.25">
@@ -12313,58 +12313,58 @@
         <v>19.225349999999999</v>
       </c>
       <c r="AK26">
-        <v>7.2040999999999994E-2</v>
+        <v>0.115234</v>
       </c>
       <c r="AL26">
-        <v>7.0805000000000007E-2</v>
+        <v>0.11329500000000001</v>
       </c>
       <c r="AM26">
-        <v>8.7060999999999999E-2</v>
+        <v>0.14228299999999999</v>
       </c>
       <c r="AN26">
-        <v>9.0768000000000001E-2</v>
+        <v>0.148204</v>
       </c>
       <c r="AO26">
-        <v>8.0613000000000004E-2</v>
+        <v>0.12820699999999999</v>
       </c>
       <c r="AP26">
-        <v>7.1815000000000004E-2</v>
+        <v>0.114715</v>
       </c>
       <c r="AQ26">
-        <v>8.0410999999999996E-2</v>
+        <v>0.128998</v>
       </c>
       <c r="AR26">
-        <v>8.0446000000000004E-2</v>
+        <v>0.12843199999999999</v>
       </c>
       <c r="AS26">
-        <v>0.113279</v>
+        <v>0.17699500000000001</v>
       </c>
       <c r="AT26">
-        <v>0.102904</v>
+        <v>0.16789999999999999</v>
       </c>
       <c r="AU26">
-        <v>9.3417E-2</v>
+        <v>0.14876700000000001</v>
       </c>
       <c r="AV26">
-        <v>8.4348999999999993E-2</v>
+        <v>0.13447100000000001</v>
       </c>
       <c r="AW26">
-        <v>0.13736599999999999</v>
+        <v>0.21851000000000001</v>
       </c>
       <c r="AX26">
-        <v>0.13736100000000001</v>
+        <v>0.22003900000000001</v>
       </c>
       <c r="AY26">
-        <v>0.176348</v>
+        <v>0.277005</v>
       </c>
       <c r="AZ26">
-        <v>0.18176300000000001</v>
+        <v>0.28703299999999998</v>
       </c>
       <c r="BA26">
-        <v>0.15864600000000001</v>
+        <v>0.25273899999999999</v>
       </c>
       <c r="BB26">
-        <v>0.14394100000000001</v>
+        <v>0.23102400000000001</v>
       </c>
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.25">
@@ -12477,58 +12477,58 @@
         <v>21.037562000000001</v>
       </c>
       <c r="AK27">
-        <v>7.1378999999999998E-2</v>
+        <v>0.11419</v>
       </c>
       <c r="AL27">
-        <v>7.0649000000000003E-2</v>
+        <v>0.11305</v>
       </c>
       <c r="AM27">
-        <v>8.6669999999999997E-2</v>
+        <v>0.14116200000000001</v>
       </c>
       <c r="AN27">
-        <v>9.0352000000000002E-2</v>
+        <v>0.147312</v>
       </c>
       <c r="AO27">
-        <v>8.0842999999999998E-2</v>
+        <v>0.12861600000000001</v>
       </c>
       <c r="AP27">
-        <v>7.1451000000000001E-2</v>
+        <v>0.114175</v>
       </c>
       <c r="AQ27">
-        <v>7.9941999999999999E-2</v>
+        <v>0.129389</v>
       </c>
       <c r="AR27">
-        <v>7.9405000000000003E-2</v>
+        <v>0.127382</v>
       </c>
       <c r="AS27">
-        <v>0.12145499999999999</v>
+        <v>0.19061900000000001</v>
       </c>
       <c r="AT27">
-        <v>0.10122399999999999</v>
+        <v>0.164324</v>
       </c>
       <c r="AU27">
-        <v>9.357E-2</v>
+        <v>0.14885899999999999</v>
       </c>
       <c r="AV27">
-        <v>8.4112999999999993E-2</v>
+        <v>0.13418099999999999</v>
       </c>
       <c r="AW27">
-        <v>0.13641</v>
+        <v>0.21734700000000001</v>
       </c>
       <c r="AX27">
-        <v>0.136879</v>
+        <v>0.21904100000000001</v>
       </c>
       <c r="AY27">
-        <v>0.18006</v>
+        <v>0.27859</v>
       </c>
       <c r="AZ27">
-        <v>0.182036</v>
+        <v>0.29062399999999999</v>
       </c>
       <c r="BA27">
-        <v>0.15926499999999999</v>
+        <v>0.253108</v>
       </c>
       <c r="BB27">
-        <v>0.14325299999999999</v>
+        <v>0.22988600000000001</v>
       </c>
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.25">
@@ -12641,58 +12641,58 @@
         <v>22.120916000000001</v>
       </c>
       <c r="AK28">
-        <v>7.0749999999999993E-2</v>
+        <v>0.113196</v>
       </c>
       <c r="AL28">
-        <v>7.0748000000000005E-2</v>
+        <v>0.11321299999999999</v>
       </c>
       <c r="AM28">
-        <v>8.3720000000000003E-2</v>
+        <v>0.133965</v>
       </c>
       <c r="AN28">
-        <v>8.7254999999999999E-2</v>
+        <v>0.140794</v>
       </c>
       <c r="AO28">
-        <v>8.0668000000000004E-2</v>
+        <v>0.12873200000000001</v>
       </c>
       <c r="AP28">
-        <v>7.1182999999999996E-2</v>
+        <v>0.113771</v>
       </c>
       <c r="AQ28">
-        <v>7.9136999999999999E-2</v>
+        <v>0.12846299999999999</v>
       </c>
       <c r="AR28">
-        <v>7.8272999999999995E-2</v>
+        <v>0.12634600000000001</v>
       </c>
       <c r="AS28">
-        <v>0.109504</v>
+        <v>0.173044</v>
       </c>
       <c r="AT28">
-        <v>9.6726000000000006E-2</v>
+        <v>0.154361</v>
       </c>
       <c r="AU28">
-        <v>9.2878000000000002E-2</v>
+        <v>0.14851700000000001</v>
       </c>
       <c r="AV28">
-        <v>8.3241999999999997E-2</v>
+        <v>0.13329299999999999</v>
       </c>
       <c r="AW28">
-        <v>0.133858</v>
+        <v>0.214249</v>
       </c>
       <c r="AX28">
-        <v>0.13566400000000001</v>
+        <v>0.21649199999999999</v>
       </c>
       <c r="AY28">
-        <v>0.16738700000000001</v>
+        <v>0.266374</v>
       </c>
       <c r="AZ28">
-        <v>0.174737</v>
+        <v>0.27949099999999999</v>
       </c>
       <c r="BA28">
-        <v>0.15833700000000001</v>
+        <v>0.251994</v>
       </c>
       <c r="BB28">
-        <v>0.141018</v>
+        <v>0.22579299999999999</v>
       </c>
     </row>
     <row r="29" spans="1:54" x14ac:dyDescent="0.25">
@@ -12805,58 +12805,58 @@
         <v>19.249687999999999</v>
       </c>
       <c r="AK29">
-        <v>7.0803000000000005E-2</v>
+        <v>0.11326899999999999</v>
       </c>
       <c r="AL29">
-        <v>7.1568999999999994E-2</v>
+        <v>0.114521</v>
       </c>
       <c r="AM29">
-        <v>8.1848000000000004E-2</v>
+        <v>0.12984999999999999</v>
       </c>
       <c r="AN29">
-        <v>8.3969000000000002E-2</v>
+        <v>0.13395799999999999</v>
       </c>
       <c r="AO29">
-        <v>8.2270999999999997E-2</v>
+        <v>0.13078699999999999</v>
       </c>
       <c r="AP29">
-        <v>7.1181999999999995E-2</v>
+        <v>0.11378000000000001</v>
       </c>
       <c r="AQ29">
-        <v>7.8326000000000007E-2</v>
+        <v>0.126583</v>
       </c>
       <c r="AR29">
-        <v>7.9490000000000005E-2</v>
+        <v>0.12762200000000001</v>
       </c>
       <c r="AS29">
-        <v>9.1925000000000007E-2</v>
+        <v>0.14685300000000001</v>
       </c>
       <c r="AT29">
-        <v>9.4447000000000003E-2</v>
+        <v>0.14982200000000001</v>
       </c>
       <c r="AU29">
-        <v>9.3170000000000003E-2</v>
+        <v>0.149141</v>
       </c>
       <c r="AV29">
-        <v>8.3296999999999996E-2</v>
+        <v>0.13348199999999999</v>
       </c>
       <c r="AW29">
-        <v>0.13290099999999999</v>
+        <v>0.213089</v>
       </c>
       <c r="AX29">
-        <v>0.13644100000000001</v>
+        <v>0.21776200000000001</v>
       </c>
       <c r="AY29">
-        <v>0.15729699999999999</v>
+        <v>0.25510100000000002</v>
       </c>
       <c r="AZ29">
-        <v>0.164795</v>
+        <v>0.26240400000000003</v>
       </c>
       <c r="BA29">
-        <v>0.15682599999999999</v>
+        <v>0.25065500000000002</v>
       </c>
       <c r="BB29">
-        <v>0.13905100000000001</v>
+        <v>0.222163</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -12969,58 +12969,58 @@
         <v>18.342462999999999</v>
       </c>
       <c r="AK30">
-        <v>7.1046999999999999E-2</v>
+        <v>0.113644</v>
       </c>
       <c r="AL30">
-        <v>7.2747999999999993E-2</v>
+        <v>0.116394</v>
       </c>
       <c r="AM30">
-        <v>8.2414000000000001E-2</v>
+        <v>0.13203400000000001</v>
       </c>
       <c r="AN30">
-        <v>8.2822000000000007E-2</v>
+        <v>0.13183900000000001</v>
       </c>
       <c r="AO30">
-        <v>8.4857000000000002E-2</v>
+        <v>0.13394900000000001</v>
       </c>
       <c r="AP30">
-        <v>7.1129999999999999E-2</v>
+        <v>0.11376500000000001</v>
       </c>
       <c r="AQ30">
-        <v>7.7817999999999998E-2</v>
+        <v>0.125582</v>
       </c>
       <c r="AR30">
-        <v>8.1730999999999998E-2</v>
+        <v>0.130028</v>
       </c>
       <c r="AS30">
-        <v>8.8469000000000006E-2</v>
+        <v>0.14219200000000001</v>
       </c>
       <c r="AT30">
-        <v>9.4397999999999996E-2</v>
+        <v>0.150196</v>
       </c>
       <c r="AU30">
-        <v>9.4833000000000001E-2</v>
+        <v>0.151056</v>
       </c>
       <c r="AV30">
-        <v>8.4370000000000001E-2</v>
+        <v>0.13486200000000001</v>
       </c>
       <c r="AW30">
-        <v>0.13361300000000001</v>
+        <v>0.21404400000000001</v>
       </c>
       <c r="AX30">
-        <v>0.139288</v>
+        <v>0.222971</v>
       </c>
       <c r="AY30">
-        <v>0.155032</v>
+        <v>0.25046499999999999</v>
       </c>
       <c r="AZ30">
-        <v>0.16292599999999999</v>
+        <v>0.26061099999999998</v>
       </c>
       <c r="BA30">
-        <v>0.157254</v>
+        <v>0.25165900000000002</v>
       </c>
       <c r="BB30">
-        <v>0.139013</v>
+        <v>0.222243</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -13133,58 +13133,58 @@
         <v>19.465841999999999</v>
       </c>
       <c r="AK31">
-        <v>7.0129999999999998E-2</v>
+        <v>0.112201</v>
       </c>
       <c r="AL31">
-        <v>7.2804999999999995E-2</v>
+        <v>0.116497</v>
       </c>
       <c r="AM31">
-        <v>8.1065999999999999E-2</v>
+        <v>0.12862399999999999</v>
       </c>
       <c r="AN31">
-        <v>8.2004999999999995E-2</v>
+        <v>0.12997500000000001</v>
       </c>
       <c r="AO31">
-        <v>8.7686E-2</v>
+        <v>0.13720499999999999</v>
       </c>
       <c r="AP31">
-        <v>7.1813000000000002E-2</v>
+        <v>0.11482299999999999</v>
       </c>
       <c r="AQ31">
-        <v>7.775E-2</v>
+        <v>0.123603</v>
       </c>
       <c r="AR31">
-        <v>8.1059000000000006E-2</v>
+        <v>0.129992</v>
       </c>
       <c r="AS31">
-        <v>8.6312E-2</v>
+        <v>0.138791</v>
       </c>
       <c r="AT31">
-        <v>9.4039999999999999E-2</v>
+        <v>0.149122</v>
       </c>
       <c r="AU31">
-        <v>9.6975000000000006E-2</v>
+        <v>0.153529</v>
       </c>
       <c r="AV31">
-        <v>8.5400000000000004E-2</v>
+        <v>0.136242</v>
       </c>
       <c r="AW31">
-        <v>0.13513500000000001</v>
+        <v>0.216053</v>
       </c>
       <c r="AX31">
-        <v>0.14038200000000001</v>
+        <v>0.22462499999999999</v>
       </c>
       <c r="AY31">
-        <v>0.14754800000000001</v>
+        <v>0.24492</v>
       </c>
       <c r="AZ31">
-        <v>0.161442</v>
+        <v>0.256496</v>
       </c>
       <c r="BA31">
-        <v>0.15787499999999999</v>
+        <v>0.253274</v>
       </c>
       <c r="BB31">
-        <v>0.13989399999999999</v>
+        <v>0.22405</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -13297,58 +13297,58 @@
         <v>22.147167</v>
       </c>
       <c r="AK32">
-        <v>6.9979E-2</v>
+        <v>0.11196200000000001</v>
       </c>
       <c r="AL32">
-        <v>7.4229000000000003E-2</v>
+        <v>0.118757</v>
       </c>
       <c r="AM32">
-        <v>8.2474000000000006E-2</v>
+        <v>0.13239200000000001</v>
       </c>
       <c r="AN32">
-        <v>8.4765999999999994E-2</v>
+        <v>0.13617099999999999</v>
       </c>
       <c r="AO32">
-        <v>8.6699999999999999E-2</v>
+        <v>0.136356</v>
       </c>
       <c r="AP32">
-        <v>7.2670999999999999E-2</v>
+        <v>0.116157</v>
       </c>
       <c r="AQ32">
-        <v>7.9413999999999998E-2</v>
+        <v>0.129443</v>
       </c>
       <c r="AR32">
-        <v>8.3344000000000001E-2</v>
+        <v>0.13267000000000001</v>
       </c>
       <c r="AS32">
-        <v>9.5542000000000002E-2</v>
+        <v>0.152417</v>
       </c>
       <c r="AT32">
-        <v>9.6970000000000001E-2</v>
+        <v>0.15587500000000001</v>
       </c>
       <c r="AU32">
-        <v>0.100102</v>
+        <v>0.156612</v>
       </c>
       <c r="AV32">
-        <v>8.6328000000000002E-2</v>
+        <v>0.137521</v>
       </c>
       <c r="AW32">
-        <v>0.13603799999999999</v>
+        <v>0.21738099999999999</v>
       </c>
       <c r="AX32">
-        <v>0.142482</v>
+        <v>0.228322</v>
       </c>
       <c r="AY32">
-        <v>0.16166700000000001</v>
+        <v>0.25692999999999999</v>
       </c>
       <c r="AZ32">
-        <v>0.16939100000000001</v>
+        <v>0.26944400000000002</v>
       </c>
       <c r="BA32">
-        <v>0.16175400000000001</v>
+        <v>0.25818200000000002</v>
       </c>
       <c r="BB32">
-        <v>0.13938200000000001</v>
+        <v>0.222916</v>
       </c>
     </row>
     <row r="33" spans="1:54" x14ac:dyDescent="0.25">
@@ -13461,58 +13461,58 @@
         <v>23.558717999999999</v>
       </c>
       <c r="AK33">
-        <v>6.973E-2</v>
+        <v>0.111572</v>
       </c>
       <c r="AL33">
-        <v>7.4937000000000004E-2</v>
+        <v>0.119882</v>
       </c>
       <c r="AM33">
-        <v>8.3387000000000003E-2</v>
+        <v>0.134769</v>
       </c>
       <c r="AN33">
-        <v>8.6426000000000003E-2</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="AO33">
-        <v>8.4013000000000004E-2</v>
+        <v>0.13355300000000001</v>
       </c>
       <c r="AP33">
-        <v>7.3044999999999999E-2</v>
+        <v>0.116781</v>
       </c>
       <c r="AQ33">
-        <v>8.0245999999999998E-2</v>
+        <v>0.13020300000000001</v>
       </c>
       <c r="AR33">
-        <v>8.4898000000000001E-2</v>
+        <v>0.134495</v>
       </c>
       <c r="AS33">
-        <v>9.9018999999999996E-2</v>
+        <v>0.15686600000000001</v>
       </c>
       <c r="AT33">
-        <v>9.8692000000000002E-2</v>
+        <v>0.15964999999999999</v>
       </c>
       <c r="AU33">
-        <v>0.100453</v>
+        <v>0.157363</v>
       </c>
       <c r="AV33">
-        <v>8.7349999999999997E-2</v>
+        <v>0.138735</v>
       </c>
       <c r="AW33">
-        <v>0.137517</v>
+        <v>0.219219</v>
       </c>
       <c r="AX33">
-        <v>0.144319</v>
+        <v>0.23174</v>
       </c>
       <c r="AY33">
-        <v>0.16887199999999999</v>
+        <v>0.264874</v>
       </c>
       <c r="AZ33">
-        <v>0.17569100000000001</v>
+        <v>0.27830899999999997</v>
       </c>
       <c r="BA33">
-        <v>0.16259599999999999</v>
+        <v>0.25988299999999998</v>
       </c>
       <c r="BB33">
-        <v>0.139511</v>
+        <v>0.22306300000000001</v>
       </c>
     </row>
     <row r="34" spans="1:54" x14ac:dyDescent="0.25">
@@ -13625,58 +13625,58 @@
         <v>21.775715999999999</v>
       </c>
       <c r="AK34">
-        <v>7.0992E-2</v>
+        <v>0.113583</v>
       </c>
       <c r="AL34">
-        <v>7.0685999999999999E-2</v>
+        <v>0.113112</v>
       </c>
       <c r="AM34">
-        <v>8.7622000000000005E-2</v>
+        <v>0.142788</v>
       </c>
       <c r="AN34">
-        <v>8.9524999999999993E-2</v>
+        <v>0.14501800000000001</v>
       </c>
       <c r="AO34">
-        <v>7.8699000000000005E-2</v>
+        <v>0.126387</v>
       </c>
       <c r="AP34">
-        <v>7.1725999999999998E-2</v>
+        <v>0.114636</v>
       </c>
       <c r="AQ34">
-        <v>8.0549999999999997E-2</v>
+        <v>0.13148299999999999</v>
       </c>
       <c r="AR34">
-        <v>8.1230999999999998E-2</v>
+        <v>0.12951699999999999</v>
       </c>
       <c r="AS34">
-        <v>0.11297</v>
+        <v>0.17655299999999999</v>
       </c>
       <c r="AT34">
-        <v>0.10377</v>
+        <v>0.168957</v>
       </c>
       <c r="AU34">
-        <v>9.3618000000000007E-2</v>
+        <v>0.14927399999999999</v>
       </c>
       <c r="AV34">
-        <v>8.4904999999999994E-2</v>
+        <v>0.13534199999999999</v>
       </c>
       <c r="AW34">
-        <v>0.136959</v>
+        <v>0.218192</v>
       </c>
       <c r="AX34">
-        <v>0.139238</v>
+        <v>0.223217</v>
       </c>
       <c r="AY34">
-        <v>0.17760200000000001</v>
+        <v>0.28098699999999999</v>
       </c>
       <c r="AZ34">
-        <v>0.179343</v>
+        <v>0.28195199999999998</v>
       </c>
       <c r="BA34">
-        <v>0.15914</v>
+        <v>0.25373400000000002</v>
       </c>
       <c r="BB34">
-        <v>0.14650099999999999</v>
+        <v>0.235878</v>
       </c>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
@@ -13789,58 +13789,58 @@
         <v>24.028524999999998</v>
       </c>
       <c r="AK35">
-        <v>7.0499000000000006E-2</v>
+        <v>0.112804</v>
       </c>
       <c r="AL35">
-        <v>7.0935999999999999E-2</v>
+        <v>0.113509</v>
       </c>
       <c r="AM35">
-        <v>8.7622000000000005E-2</v>
+        <v>0.14261099999999999</v>
       </c>
       <c r="AN35">
-        <v>8.9005000000000001E-2</v>
+        <v>0.143874</v>
       </c>
       <c r="AO35">
-        <v>7.8581999999999999E-2</v>
+        <v>0.12642400000000001</v>
       </c>
       <c r="AP35">
-        <v>7.1387000000000006E-2</v>
+        <v>0.114145</v>
       </c>
       <c r="AQ35">
-        <v>7.9171000000000005E-2</v>
+        <v>0.126112</v>
       </c>
       <c r="AR35">
-        <v>8.0641000000000004E-2</v>
+        <v>0.12898100000000001</v>
       </c>
       <c r="AS35">
-        <v>0.114416</v>
+        <v>0.17957300000000001</v>
       </c>
       <c r="AT35">
-        <v>0.102628</v>
+        <v>0.166521</v>
       </c>
       <c r="AU35">
-        <v>9.3092999999999995E-2</v>
+        <v>0.148947</v>
       </c>
       <c r="AV35">
-        <v>8.4654999999999994E-2</v>
+        <v>0.13508300000000001</v>
       </c>
       <c r="AW35">
-        <v>0.13553599999999999</v>
+        <v>0.21650900000000001</v>
       </c>
       <c r="AX35">
-        <v>0.138931</v>
+        <v>0.22247400000000001</v>
       </c>
       <c r="AY35">
-        <v>0.178341</v>
+        <v>0.28146500000000002</v>
       </c>
       <c r="AZ35">
-        <v>0.178009</v>
+        <v>0.28122599999999998</v>
       </c>
       <c r="BA35">
-        <v>0.157775</v>
+        <v>0.25237100000000001</v>
       </c>
       <c r="BB35">
-        <v>0.145679</v>
+        <v>0.23436100000000001</v>
       </c>
     </row>
     <row r="36" spans="1:54" x14ac:dyDescent="0.25">
@@ -13953,58 +13953,58 @@
         <v>24.047395999999999</v>
       </c>
       <c r="AK36">
-        <v>7.0137000000000005E-2</v>
+        <v>0.11222699999999999</v>
       </c>
       <c r="AL36">
-        <v>7.1775000000000005E-2</v>
+        <v>0.114843</v>
       </c>
       <c r="AM36">
-        <v>8.6610999999999994E-2</v>
+        <v>0.14036599999999999</v>
       </c>
       <c r="AN36">
-        <v>8.7112999999999996E-2</v>
+        <v>0.140072</v>
       </c>
       <c r="AO36">
-        <v>7.9642000000000004E-2</v>
+        <v>0.127833</v>
       </c>
       <c r="AP36">
-        <v>7.1472999999999995E-2</v>
+        <v>0.114262</v>
       </c>
       <c r="AQ36">
-        <v>7.7812999999999993E-2</v>
+        <v>0.12300899999999999</v>
       </c>
       <c r="AR36">
-        <v>8.0609E-2</v>
+        <v>0.12904499999999999</v>
       </c>
       <c r="AS36">
-        <v>0.107207</v>
+        <v>0.169159</v>
       </c>
       <c r="AT36">
-        <v>9.9858000000000002E-2</v>
+        <v>0.16073299999999999</v>
       </c>
       <c r="AU36">
-        <v>9.2893000000000003E-2</v>
+        <v>0.14892</v>
       </c>
       <c r="AV36">
-        <v>8.3955000000000002E-2</v>
+        <v>0.134408</v>
       </c>
       <c r="AW36">
-        <v>0.13361300000000001</v>
+        <v>0.21416399999999999</v>
       </c>
       <c r="AX36">
-        <v>0.13975899999999999</v>
+        <v>0.223861</v>
       </c>
       <c r="AY36">
-        <v>0.176838</v>
+        <v>0.27854800000000002</v>
       </c>
       <c r="AZ36">
-        <v>0.17439499999999999</v>
+        <v>0.27670099999999997</v>
       </c>
       <c r="BA36">
-        <v>0.157523</v>
+        <v>0.25204799999999999</v>
       </c>
       <c r="BB36">
-        <v>0.14357400000000001</v>
+        <v>0.23052300000000001</v>
       </c>
     </row>
     <row r="37" spans="1:54" x14ac:dyDescent="0.25">
@@ -14117,58 +14117,58 @@
         <v>20.426462999999998</v>
       </c>
       <c r="AK37">
-        <v>6.9808999999999996E-2</v>
+        <v>0.111707</v>
       </c>
       <c r="AL37">
-        <v>7.3248999999999995E-2</v>
+        <v>0.11718099999999999</v>
       </c>
       <c r="AM37">
-        <v>8.5400000000000004E-2</v>
+        <v>0.13787099999999999</v>
       </c>
       <c r="AN37">
-        <v>8.4889999999999993E-2</v>
+        <v>0.13562199999999999</v>
       </c>
       <c r="AO37">
-        <v>8.1382999999999997E-2</v>
+        <v>0.130021</v>
       </c>
       <c r="AP37">
-        <v>7.1637000000000006E-2</v>
+        <v>0.11451</v>
       </c>
       <c r="AQ37">
-        <v>7.7340999999999993E-2</v>
+        <v>0.123707</v>
       </c>
       <c r="AR37">
-        <v>8.2506999999999997E-2</v>
+        <v>0.13092000000000001</v>
       </c>
       <c r="AS37">
-        <v>0.10009800000000001</v>
+        <v>0.158973</v>
       </c>
       <c r="AT37">
-        <v>9.7455E-2</v>
+        <v>0.15584100000000001</v>
       </c>
       <c r="AU37">
-        <v>9.2998999999999998E-2</v>
+        <v>0.14926900000000001</v>
       </c>
       <c r="AV37">
-        <v>8.3750000000000005E-2</v>
+        <v>0.13433600000000001</v>
       </c>
       <c r="AW37">
-        <v>0.133352</v>
+        <v>0.21379999999999999</v>
       </c>
       <c r="AX37">
-        <v>0.14267199999999999</v>
+        <v>0.22935700000000001</v>
       </c>
       <c r="AY37">
-        <v>0.17525499999999999</v>
+        <v>0.27426</v>
       </c>
       <c r="AZ37">
-        <v>0.17075399999999999</v>
+        <v>0.27177600000000002</v>
       </c>
       <c r="BA37">
-        <v>0.15809000000000001</v>
+        <v>0.25267400000000001</v>
       </c>
       <c r="BB37">
-        <v>0.140156</v>
+        <v>0.22403000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:54" x14ac:dyDescent="0.25">
@@ -14281,58 +14281,58 @@
         <v>18.440173999999999</v>
       </c>
       <c r="AK38">
-        <v>6.9773000000000002E-2</v>
+        <v>0.11164399999999999</v>
       </c>
       <c r="AL38">
-        <v>7.3809E-2</v>
+        <v>0.118076</v>
       </c>
       <c r="AM38">
-        <v>8.4613999999999995E-2</v>
+        <v>0.13648399999999999</v>
       </c>
       <c r="AN38">
-        <v>8.3787E-2</v>
+        <v>0.133601</v>
       </c>
       <c r="AO38">
-        <v>8.2206000000000001E-2</v>
+        <v>0.13131999999999999</v>
       </c>
       <c r="AP38">
-        <v>7.1606000000000003E-2</v>
+        <v>0.114507</v>
       </c>
       <c r="AQ38">
-        <v>7.6965000000000006E-2</v>
+        <v>0.123504</v>
       </c>
       <c r="AR38">
-        <v>8.2030000000000006E-2</v>
+        <v>0.13078400000000001</v>
       </c>
       <c r="AS38">
-        <v>9.5298999999999995E-2</v>
+        <v>0.15206500000000001</v>
       </c>
       <c r="AT38">
-        <v>9.6282000000000006E-2</v>
+        <v>0.153617</v>
       </c>
       <c r="AU38">
-        <v>9.2161000000000007E-2</v>
+        <v>0.149283</v>
       </c>
       <c r="AV38">
-        <v>8.5320999999999994E-2</v>
+        <v>0.13612099999999999</v>
       </c>
       <c r="AW38">
-        <v>0.13328300000000001</v>
+        <v>0.21379699999999999</v>
       </c>
       <c r="AX38">
-        <v>0.143877</v>
+        <v>0.23134199999999999</v>
       </c>
       <c r="AY38">
-        <v>0.170685</v>
+        <v>0.26769300000000001</v>
       </c>
       <c r="AZ38">
-        <v>0.16969600000000001</v>
+        <v>0.27128400000000003</v>
       </c>
       <c r="BA38">
-        <v>0.15757499999999999</v>
+        <v>0.25261099999999997</v>
       </c>
       <c r="BB38">
-        <v>0.138322</v>
+        <v>0.220634</v>
       </c>
     </row>
     <row r="39" spans="1:54" x14ac:dyDescent="0.25">
@@ -14445,58 +14445,58 @@
         <v>21.805916</v>
       </c>
       <c r="AK39">
-        <v>6.9363999999999995E-2</v>
+        <v>0.110998</v>
       </c>
       <c r="AL39">
-        <v>7.3543999999999998E-2</v>
+        <v>0.117669</v>
       </c>
       <c r="AM39">
-        <v>8.3089999999999997E-2</v>
+        <v>0.13278200000000001</v>
       </c>
       <c r="AN39">
-        <v>8.3334000000000005E-2</v>
+        <v>0.132692</v>
       </c>
       <c r="AO39">
-        <v>8.3630999999999997E-2</v>
+        <v>0.133077</v>
       </c>
       <c r="AP39">
-        <v>7.2416999999999995E-2</v>
+        <v>0.115714</v>
       </c>
       <c r="AQ39">
-        <v>7.6399999999999996E-2</v>
+        <v>0.118171</v>
       </c>
       <c r="AR39">
-        <v>8.0294000000000004E-2</v>
+        <v>0.12964200000000001</v>
       </c>
       <c r="AS39">
-        <v>9.0844999999999995E-2</v>
+        <v>0.145125</v>
       </c>
       <c r="AT39">
-        <v>9.5527000000000001E-2</v>
+        <v>0.15181</v>
       </c>
       <c r="AU39">
-        <v>9.3282000000000004E-2</v>
+        <v>0.15079799999999999</v>
       </c>
       <c r="AV39">
-        <v>8.5668999999999995E-2</v>
+        <v>0.13675200000000001</v>
       </c>
       <c r="AW39">
-        <v>0.13373299999999999</v>
+        <v>0.21451899999999999</v>
       </c>
       <c r="AX39">
-        <v>0.14404500000000001</v>
+        <v>0.23123199999999999</v>
       </c>
       <c r="AY39">
-        <v>0.15585599999999999</v>
+        <v>0.25632199999999999</v>
       </c>
       <c r="AZ39">
-        <v>0.16642199999999999</v>
+        <v>0.26362799999999997</v>
       </c>
       <c r="BA39">
-        <v>0.15768799999999999</v>
+        <v>0.25352000000000002</v>
       </c>
       <c r="BB39">
-        <v>0.13866700000000001</v>
+        <v>0.221499</v>
       </c>
     </row>
     <row r="40" spans="1:54" x14ac:dyDescent="0.25">
@@ -14609,58 +14609,58 @@
         <v>21.411072000000001</v>
       </c>
       <c r="AK40">
-        <v>6.966E-2</v>
+        <v>0.111458</v>
       </c>
       <c r="AL40">
-        <v>7.4839000000000003E-2</v>
+        <v>0.11972099999999999</v>
       </c>
       <c r="AM40">
-        <v>8.4002999999999994E-2</v>
+        <v>0.13547699999999999</v>
       </c>
       <c r="AN40">
-        <v>8.4589999999999999E-2</v>
+        <v>0.13549600000000001</v>
       </c>
       <c r="AO40">
-        <v>8.3759E-2</v>
+        <v>0.13325600000000001</v>
       </c>
       <c r="AP40">
-        <v>7.2163000000000005E-2</v>
+        <v>0.115414</v>
       </c>
       <c r="AQ40">
-        <v>7.8171000000000004E-2</v>
+        <v>0.12557199999999999</v>
       </c>
       <c r="AR40">
-        <v>8.3467E-2</v>
+        <v>0.13289699999999999</v>
       </c>
       <c r="AS40">
-        <v>9.9485000000000004E-2</v>
+        <v>0.15806000000000001</v>
       </c>
       <c r="AT40">
-        <v>9.7202999999999998E-2</v>
+        <v>0.155671</v>
       </c>
       <c r="AU40">
-        <v>9.6539E-2</v>
+        <v>0.15365999999999999</v>
       </c>
       <c r="AV40">
-        <v>8.5875000000000007E-2</v>
+        <v>0.13722400000000001</v>
       </c>
       <c r="AW40">
-        <v>0.137049</v>
+        <v>0.21856</v>
       </c>
       <c r="AX40">
-        <v>0.14732700000000001</v>
+        <v>0.237486</v>
       </c>
       <c r="AY40">
-        <v>0.16476199999999999</v>
+        <v>0.26313900000000001</v>
       </c>
       <c r="AZ40">
-        <v>0.17199999999999999</v>
+        <v>0.27259699999999998</v>
       </c>
       <c r="BA40">
-        <v>0.16369500000000001</v>
+        <v>0.26008799999999999</v>
       </c>
       <c r="BB40">
-        <v>0.13802900000000001</v>
+        <v>0.220224</v>
       </c>
     </row>
     <row r="41" spans="1:54" x14ac:dyDescent="0.25">
@@ -14773,58 +14773,58 @@
         <v>22.710896000000002</v>
       </c>
       <c r="AK41">
-        <v>6.9595000000000004E-2</v>
+        <v>0.111358</v>
       </c>
       <c r="AL41">
-        <v>7.5076000000000004E-2</v>
+        <v>0.1201</v>
       </c>
       <c r="AM41">
-        <v>8.4043999999999994E-2</v>
+        <v>0.13572400000000001</v>
       </c>
       <c r="AN41">
-        <v>8.5807999999999995E-2</v>
+        <v>0.138214</v>
       </c>
       <c r="AO41">
-        <v>8.1927E-2</v>
+        <v>0.13130700000000001</v>
       </c>
       <c r="AP41">
-        <v>7.1604000000000001E-2</v>
+        <v>0.114673</v>
       </c>
       <c r="AQ41">
-        <v>7.9240000000000005E-2</v>
+        <v>0.127584</v>
       </c>
       <c r="AR41">
-        <v>8.4807999999999995E-2</v>
+        <v>0.13441700000000001</v>
       </c>
       <c r="AS41">
-        <v>0.10036399999999999</v>
+        <v>0.15867800000000001</v>
       </c>
       <c r="AT41">
-        <v>9.8739999999999994E-2</v>
+        <v>0.15918199999999999</v>
       </c>
       <c r="AU41">
-        <v>9.6884999999999999E-2</v>
+        <v>0.15432299999999999</v>
       </c>
       <c r="AV41">
-        <v>8.7290999999999994E-2</v>
+        <v>0.138761</v>
       </c>
       <c r="AW41">
-        <v>0.13803000000000001</v>
+        <v>0.21979699999999999</v>
       </c>
       <c r="AX41">
-        <v>0.14741000000000001</v>
+        <v>0.23751700000000001</v>
       </c>
       <c r="AY41">
-        <v>0.170347</v>
+        <v>0.26859100000000002</v>
       </c>
       <c r="AZ41">
-        <v>0.17771200000000001</v>
+        <v>0.28118900000000002</v>
       </c>
       <c r="BA41">
-        <v>0.16411400000000001</v>
+        <v>0.26120199999999999</v>
       </c>
       <c r="BB41">
-        <v>0.137457</v>
+        <v>0.21898400000000001</v>
       </c>
     </row>
   </sheetData>
